--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/France Ligue 1_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/France Ligue 1_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="944" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="962" uniqueCount="280">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -595,6 +595,15 @@
     <t>['12', '47']</t>
   </si>
   <si>
+    <t>['8', '25']</t>
+  </si>
+  <si>
+    <t>['34', '71']</t>
+  </si>
+  <si>
+    <t>['43']</t>
+  </si>
+  <si>
     <t>['3', '84', '86', '90']</t>
   </si>
   <si>
@@ -836,6 +845,15 @@
   </si>
   <si>
     <t>['52', '59']</t>
+  </si>
+  <si>
+    <t>['45+2']</t>
+  </si>
+  <si>
+    <t>['28', '44', '64', '86']</t>
+  </si>
+  <si>
+    <t>['45', '49']</t>
   </si>
 </sst>
 </file>
@@ -1197,7 +1215,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP147"/>
+  <dimension ref="A1:BP150"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1453,7 +1471,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Q2">
         <v>6</v>
@@ -1659,7 +1677,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Q3">
         <v>3.4</v>
@@ -1737,10 +1755,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ3">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1865,7 +1883,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -1943,7 +1961,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AQ4">
         <v>1.56</v>
@@ -2277,7 +2295,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q6">
         <v>3.75</v>
@@ -2358,7 +2376,7 @@
         <v>2</v>
       </c>
       <c r="AQ6">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2483,7 +2501,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -3179,10 +3197,10 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ10">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3513,7 +3531,7 @@
         <v>90</v>
       </c>
       <c r="P12" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="Q12">
         <v>2.8</v>
@@ -3925,7 +3943,7 @@
         <v>90</v>
       </c>
       <c r="P14" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q14">
         <v>2.65</v>
@@ -4337,7 +4355,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q16">
         <v>3.6</v>
@@ -4955,7 +4973,7 @@
         <v>101</v>
       </c>
       <c r="P19" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q19">
         <v>2.1</v>
@@ -5161,7 +5179,7 @@
         <v>102</v>
       </c>
       <c r="P20" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Q20">
         <v>2.45</v>
@@ -5445,7 +5463,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ21">
         <v>0.13</v>
@@ -5573,7 +5591,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q22">
         <v>2.8</v>
@@ -5779,7 +5797,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="Q23">
         <v>4.2</v>
@@ -5860,7 +5878,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ23">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
       <c r="AR23">
         <v>1.52</v>
@@ -5985,7 +6003,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q24">
         <v>2.4</v>
@@ -6191,7 +6209,7 @@
         <v>93</v>
       </c>
       <c r="P25" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q25">
         <v>4.5</v>
@@ -6272,7 +6290,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ25">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR25">
         <v>1.11</v>
@@ -6603,7 +6621,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q27">
         <v>3.4</v>
@@ -6681,7 +6699,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AQ27">
         <v>0.13</v>
@@ -6809,7 +6827,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q28">
         <v>4.33</v>
@@ -7302,7 +7320,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ30">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR30">
         <v>2.21</v>
@@ -7427,7 +7445,7 @@
         <v>90</v>
       </c>
       <c r="P31" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q31">
         <v>3.75</v>
@@ -7917,7 +7935,7 @@
         <v>0</v>
       </c>
       <c r="AP33">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ33">
         <v>0</v>
@@ -8045,7 +8063,7 @@
         <v>114</v>
       </c>
       <c r="P34" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="Q34">
         <v>2.3</v>
@@ -8251,7 +8269,7 @@
         <v>91</v>
       </c>
       <c r="P35" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -8744,7 +8762,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ37">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR37">
         <v>2.03</v>
@@ -9075,7 +9093,7 @@
         <v>117</v>
       </c>
       <c r="P39" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q39">
         <v>2.2</v>
@@ -9281,7 +9299,7 @@
         <v>118</v>
       </c>
       <c r="P40" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9359,7 +9377,7 @@
         <v>2</v>
       </c>
       <c r="AP40">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ40">
         <v>1.63</v>
@@ -9487,7 +9505,7 @@
         <v>119</v>
       </c>
       <c r="P41" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="Q41">
         <v>6</v>
@@ -9565,7 +9583,7 @@
         <v>3</v>
       </c>
       <c r="AP41">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AQ41">
         <v>2.25</v>
@@ -9977,7 +9995,7 @@
         <v>1</v>
       </c>
       <c r="AP43">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ43">
         <v>1.25</v>
@@ -10105,7 +10123,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Q44">
         <v>3.75</v>
@@ -10311,7 +10329,7 @@
         <v>122</v>
       </c>
       <c r="P45" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q45">
         <v>2.88</v>
@@ -10517,7 +10535,7 @@
         <v>123</v>
       </c>
       <c r="P46" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q46">
         <v>3.25</v>
@@ -10598,7 +10616,7 @@
         <v>2</v>
       </c>
       <c r="AQ46">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
       <c r="AR46">
         <v>1.4</v>
@@ -10929,7 +10947,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q48">
         <v>1.83</v>
@@ -11216,7 +11234,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ49">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR49">
         <v>1.83</v>
@@ -11341,7 +11359,7 @@
         <v>90</v>
       </c>
       <c r="P50" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q50">
         <v>5</v>
@@ -11547,7 +11565,7 @@
         <v>126</v>
       </c>
       <c r="P51" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q51">
         <v>1.8</v>
@@ -11753,7 +11771,7 @@
         <v>127</v>
       </c>
       <c r="P52" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q52">
         <v>3.1</v>
@@ -11834,7 +11852,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ52">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR52">
         <v>1.24</v>
@@ -11959,7 +11977,7 @@
         <v>128</v>
       </c>
       <c r="P53" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q53">
         <v>2.3</v>
@@ -12165,7 +12183,7 @@
         <v>106</v>
       </c>
       <c r="P54" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Q54">
         <v>4</v>
@@ -12452,7 +12470,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ55">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
       <c r="AR55">
         <v>1.26</v>
@@ -12783,7 +12801,7 @@
         <v>131</v>
       </c>
       <c r="P57" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q57">
         <v>3.25</v>
@@ -13195,7 +13213,7 @@
         <v>133</v>
       </c>
       <c r="P59" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Q59">
         <v>3.2</v>
@@ -13273,7 +13291,7 @@
         <v>3</v>
       </c>
       <c r="AP59">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ59">
         <v>1.75</v>
@@ -13685,7 +13703,7 @@
         <v>1</v>
       </c>
       <c r="AP61">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ61">
         <v>0.75</v>
@@ -13813,7 +13831,7 @@
         <v>136</v>
       </c>
       <c r="P62" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q62">
         <v>3.4</v>
@@ -14019,7 +14037,7 @@
         <v>137</v>
       </c>
       <c r="P63" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="Q63">
         <v>2.38</v>
@@ -14097,7 +14115,7 @@
         <v>0</v>
       </c>
       <c r="AP63">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AQ63">
         <v>0</v>
@@ -14225,7 +14243,7 @@
         <v>138</v>
       </c>
       <c r="P64" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q64">
         <v>4.75</v>
@@ -14637,7 +14655,7 @@
         <v>139</v>
       </c>
       <c r="P66" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q66">
         <v>3.4</v>
@@ -14715,7 +14733,7 @@
         <v>0</v>
       </c>
       <c r="AP66">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ66">
         <v>0.13</v>
@@ -14843,7 +14861,7 @@
         <v>90</v>
       </c>
       <c r="P67" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q67">
         <v>5.5</v>
@@ -15049,7 +15067,7 @@
         <v>140</v>
       </c>
       <c r="P68" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q68">
         <v>1.73</v>
@@ -15255,7 +15273,7 @@
         <v>90</v>
       </c>
       <c r="P69" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q69">
         <v>4</v>
@@ -15336,7 +15354,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ69">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR69">
         <v>1.32</v>
@@ -15461,7 +15479,7 @@
         <v>141</v>
       </c>
       <c r="P70" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q70">
         <v>2.1</v>
@@ -15667,7 +15685,7 @@
         <v>93</v>
       </c>
       <c r="P71" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q71">
         <v>3.6</v>
@@ -15748,7 +15766,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ71">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR71">
         <v>1.52</v>
@@ -15873,7 +15891,7 @@
         <v>142</v>
       </c>
       <c r="P72" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q72">
         <v>3.1</v>
@@ -16079,7 +16097,7 @@
         <v>90</v>
       </c>
       <c r="P73" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="Q73">
         <v>4.33</v>
@@ -16160,7 +16178,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ73">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
       <c r="AR73">
         <v>1.44</v>
@@ -16363,7 +16381,7 @@
         <v>0.75</v>
       </c>
       <c r="AP74">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ74">
         <v>0.75</v>
@@ -16491,7 +16509,7 @@
         <v>143</v>
       </c>
       <c r="P75" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q75">
         <v>3</v>
@@ -16697,7 +16715,7 @@
         <v>144</v>
       </c>
       <c r="P76" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -16775,7 +16793,7 @@
         <v>0</v>
       </c>
       <c r="AP76">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AQ76">
         <v>0.38</v>
@@ -16903,7 +16921,7 @@
         <v>90</v>
       </c>
       <c r="P77" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17109,7 +17127,7 @@
         <v>145</v>
       </c>
       <c r="P78" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q78">
         <v>2.1</v>
@@ -17315,7 +17333,7 @@
         <v>90</v>
       </c>
       <c r="P79" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q79">
         <v>3.5</v>
@@ -17521,7 +17539,7 @@
         <v>146</v>
       </c>
       <c r="P80" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q80">
         <v>2.63</v>
@@ -17933,7 +17951,7 @@
         <v>90</v>
       </c>
       <c r="P82" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q82">
         <v>3.6</v>
@@ -18426,7 +18444,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ84">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR84">
         <v>1.48</v>
@@ -18757,7 +18775,7 @@
         <v>90</v>
       </c>
       <c r="P86" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q86">
         <v>3.2</v>
@@ -18835,10 +18853,10 @@
         <v>1</v>
       </c>
       <c r="AP86">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ86">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR86">
         <v>1.37</v>
@@ -19787,7 +19805,7 @@
         <v>153</v>
       </c>
       <c r="P91" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q91">
         <v>4.33</v>
@@ -19868,7 +19886,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ91">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
       <c r="AR91">
         <v>1.49</v>
@@ -19993,7 +20011,7 @@
         <v>154</v>
       </c>
       <c r="P92" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q92">
         <v>1.91</v>
@@ -20199,7 +20217,7 @@
         <v>144</v>
       </c>
       <c r="P93" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -20405,7 +20423,7 @@
         <v>155</v>
       </c>
       <c r="P94" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -20611,7 +20629,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q95">
         <v>8.5</v>
@@ -20817,7 +20835,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q96">
         <v>3.2</v>
@@ -21023,7 +21041,7 @@
         <v>90</v>
       </c>
       <c r="P97" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q97">
         <v>2.88</v>
@@ -21101,7 +21119,7 @@
         <v>1</v>
       </c>
       <c r="AP97">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ97">
         <v>1.25</v>
@@ -21229,7 +21247,7 @@
         <v>158</v>
       </c>
       <c r="P98" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q98">
         <v>3.5</v>
@@ -21435,7 +21453,7 @@
         <v>90</v>
       </c>
       <c r="P99" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q99">
         <v>3.75</v>
@@ -21847,7 +21865,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q101">
         <v>2.05</v>
@@ -22259,7 +22277,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22340,7 +22358,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ103">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
       <c r="AR103">
         <v>1.68</v>
@@ -22749,10 +22767,10 @@
         <v>1.6</v>
       </c>
       <c r="AP105">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AQ105">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR105">
         <v>1.09</v>
@@ -23289,7 +23307,7 @@
         <v>90</v>
       </c>
       <c r="P108" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q108">
         <v>2.6</v>
@@ -23495,7 +23513,7 @@
         <v>166</v>
       </c>
       <c r="P109" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q109">
         <v>2.38</v>
@@ -23701,7 +23719,7 @@
         <v>90</v>
       </c>
       <c r="P110" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q110">
         <v>3.4</v>
@@ -23779,7 +23797,7 @@
         <v>1.5</v>
       </c>
       <c r="AP110">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AQ110">
         <v>1.63</v>
@@ -23985,7 +24003,7 @@
         <v>0.17</v>
       </c>
       <c r="AP111">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ111">
         <v>0.13</v>
@@ -24113,7 +24131,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q112">
         <v>2.88</v>
@@ -24191,7 +24209,7 @@
         <v>0.33</v>
       </c>
       <c r="AP112">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ112">
         <v>0.63</v>
@@ -24525,7 +24543,7 @@
         <v>170</v>
       </c>
       <c r="P114" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q114">
         <v>4.33</v>
@@ -24731,7 +24749,7 @@
         <v>90</v>
       </c>
       <c r="P115" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q115">
         <v>3</v>
@@ -25143,7 +25161,7 @@
         <v>172</v>
       </c>
       <c r="P117" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q117">
         <v>2.6</v>
@@ -25224,7 +25242,7 @@
         <v>2</v>
       </c>
       <c r="AQ117">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR117">
         <v>1.77</v>
@@ -25349,7 +25367,7 @@
         <v>173</v>
       </c>
       <c r="P118" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q118">
         <v>3.1</v>
@@ -26173,7 +26191,7 @@
         <v>176</v>
       </c>
       <c r="P122" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q122">
         <v>2.05</v>
@@ -26379,7 +26397,7 @@
         <v>90</v>
       </c>
       <c r="P123" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q123">
         <v>4.75</v>
@@ -26460,7 +26478,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ123">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR123">
         <v>1.29</v>
@@ -27203,7 +27221,7 @@
         <v>90</v>
       </c>
       <c r="P127" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q127">
         <v>5</v>
@@ -27284,7 +27302,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ127">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
       <c r="AR127">
         <v>1.3</v>
@@ -27615,7 +27633,7 @@
         <v>148</v>
       </c>
       <c r="P129" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q129">
         <v>2.88</v>
@@ -27821,7 +27839,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q130">
         <v>4.33</v>
@@ -28105,7 +28123,7 @@
         <v>2</v>
       </c>
       <c r="AP131">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AQ131">
         <v>1.75</v>
@@ -28233,7 +28251,7 @@
         <v>181</v>
       </c>
       <c r="P132" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q132">
         <v>3.5</v>
@@ -28314,7 +28332,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ132">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR132">
         <v>1.36</v>
@@ -28439,7 +28457,7 @@
         <v>90</v>
       </c>
       <c r="P133" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q133">
         <v>3.5</v>
@@ -28723,7 +28741,7 @@
         <v>0.86</v>
       </c>
       <c r="AP134">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ134">
         <v>0.78</v>
@@ -28929,7 +28947,7 @@
         <v>1.29</v>
       </c>
       <c r="AP135">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ135">
         <v>1.13</v>
@@ -29138,7 +29156,7 @@
         <v>2.75</v>
       </c>
       <c r="AQ136">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR136">
         <v>2.35</v>
@@ -29263,7 +29281,7 @@
         <v>185</v>
       </c>
       <c r="P137" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q137">
         <v>3.4</v>
@@ -29469,7 +29487,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q138">
         <v>2.88</v>
@@ -29675,7 +29693,7 @@
         <v>187</v>
       </c>
       <c r="P139" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q139">
         <v>4</v>
@@ -29881,7 +29899,7 @@
         <v>129</v>
       </c>
       <c r="P140" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q140">
         <v>2.2</v>
@@ -30911,7 +30929,7 @@
         <v>191</v>
       </c>
       <c r="P145" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q145">
         <v>1.8</v>
@@ -31117,7 +31135,7 @@
         <v>192</v>
       </c>
       <c r="P146" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q146">
         <v>4.33</v>
@@ -31422,16 +31440,16 @@
         <v>6</v>
       </c>
       <c r="AW147">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AX147">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="AY147">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ147">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="BA147">
         <v>6</v>
@@ -31480,6 +31498,624 @@
       </c>
       <c r="BP147">
         <v>1.21</v>
+      </c>
+    </row>
+    <row r="148" spans="1:68">
+      <c r="A148" s="1">
+        <v>147</v>
+      </c>
+      <c r="B148">
+        <v>7468506</v>
+      </c>
+      <c r="C148" t="s">
+        <v>68</v>
+      </c>
+      <c r="D148" t="s">
+        <v>69</v>
+      </c>
+      <c r="E148" s="2">
+        <v>45668.54166666666</v>
+      </c>
+      <c r="F148">
+        <v>17</v>
+      </c>
+      <c r="G148" t="s">
+        <v>71</v>
+      </c>
+      <c r="H148" t="s">
+        <v>80</v>
+      </c>
+      <c r="I148">
+        <v>2</v>
+      </c>
+      <c r="J148">
+        <v>1</v>
+      </c>
+      <c r="K148">
+        <v>3</v>
+      </c>
+      <c r="L148">
+        <v>2</v>
+      </c>
+      <c r="M148">
+        <v>1</v>
+      </c>
+      <c r="N148">
+        <v>3</v>
+      </c>
+      <c r="O148" t="s">
+        <v>193</v>
+      </c>
+      <c r="P148" t="s">
+        <v>277</v>
+      </c>
+      <c r="Q148">
+        <v>3.6</v>
+      </c>
+      <c r="R148">
+        <v>2.25</v>
+      </c>
+      <c r="S148">
+        <v>2.75</v>
+      </c>
+      <c r="T148">
+        <v>1.33</v>
+      </c>
+      <c r="U148">
+        <v>3.25</v>
+      </c>
+      <c r="V148">
+        <v>2.63</v>
+      </c>
+      <c r="W148">
+        <v>1.44</v>
+      </c>
+      <c r="X148">
+        <v>6.5</v>
+      </c>
+      <c r="Y148">
+        <v>1.11</v>
+      </c>
+      <c r="Z148">
+        <v>3.1</v>
+      </c>
+      <c r="AA148">
+        <v>3.5</v>
+      </c>
+      <c r="AB148">
+        <v>2.1</v>
+      </c>
+      <c r="AC148">
+        <v>1.04</v>
+      </c>
+      <c r="AD148">
+        <v>13</v>
+      </c>
+      <c r="AE148">
+        <v>1.24</v>
+      </c>
+      <c r="AF148">
+        <v>4.2</v>
+      </c>
+      <c r="AG148">
+        <v>1.63</v>
+      </c>
+      <c r="AH148">
+        <v>2.1</v>
+      </c>
+      <c r="AI148">
+        <v>1.62</v>
+      </c>
+      <c r="AJ148">
+        <v>2.2</v>
+      </c>
+      <c r="AK148">
+        <v>1.66</v>
+      </c>
+      <c r="AL148">
+        <v>1.28</v>
+      </c>
+      <c r="AM148">
+        <v>1.35</v>
+      </c>
+      <c r="AN148">
+        <v>2</v>
+      </c>
+      <c r="AO148">
+        <v>1.5</v>
+      </c>
+      <c r="AP148">
+        <v>2.11</v>
+      </c>
+      <c r="AQ148">
+        <v>1.33</v>
+      </c>
+      <c r="AR148">
+        <v>1.48</v>
+      </c>
+      <c r="AS148">
+        <v>1.28</v>
+      </c>
+      <c r="AT148">
+        <v>2.76</v>
+      </c>
+      <c r="AU148">
+        <v>7</v>
+      </c>
+      <c r="AV148">
+        <v>5</v>
+      </c>
+      <c r="AW148">
+        <v>5</v>
+      </c>
+      <c r="AX148">
+        <v>5</v>
+      </c>
+      <c r="AY148">
+        <v>14</v>
+      </c>
+      <c r="AZ148">
+        <v>12</v>
+      </c>
+      <c r="BA148">
+        <v>4</v>
+      </c>
+      <c r="BB148">
+        <v>7</v>
+      </c>
+      <c r="BC148">
+        <v>11</v>
+      </c>
+      <c r="BD148">
+        <v>2.12</v>
+      </c>
+      <c r="BE148">
+        <v>6.25</v>
+      </c>
+      <c r="BF148">
+        <v>1.9</v>
+      </c>
+      <c r="BG148">
+        <v>1.44</v>
+      </c>
+      <c r="BH148">
+        <v>2.55</v>
+      </c>
+      <c r="BI148">
+        <v>1.72</v>
+      </c>
+      <c r="BJ148">
+        <v>1.98</v>
+      </c>
+      <c r="BK148">
+        <v>2.17</v>
+      </c>
+      <c r="BL148">
+        <v>1.6</v>
+      </c>
+      <c r="BM148">
+        <v>2.8</v>
+      </c>
+      <c r="BN148">
+        <v>1.36</v>
+      </c>
+      <c r="BO148">
+        <v>3.8</v>
+      </c>
+      <c r="BP148">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="149" spans="1:68">
+      <c r="A149" s="1">
+        <v>148</v>
+      </c>
+      <c r="B149">
+        <v>7468503</v>
+      </c>
+      <c r="C149" t="s">
+        <v>68</v>
+      </c>
+      <c r="D149" t="s">
+        <v>69</v>
+      </c>
+      <c r="E149" s="2">
+        <v>45668.625</v>
+      </c>
+      <c r="F149">
+        <v>17</v>
+      </c>
+      <c r="G149" t="s">
+        <v>72</v>
+      </c>
+      <c r="H149" t="s">
+        <v>86</v>
+      </c>
+      <c r="I149">
+        <v>1</v>
+      </c>
+      <c r="J149">
+        <v>2</v>
+      </c>
+      <c r="K149">
+        <v>3</v>
+      </c>
+      <c r="L149">
+        <v>2</v>
+      </c>
+      <c r="M149">
+        <v>4</v>
+      </c>
+      <c r="N149">
+        <v>6</v>
+      </c>
+      <c r="O149" t="s">
+        <v>194</v>
+      </c>
+      <c r="P149" t="s">
+        <v>278</v>
+      </c>
+      <c r="Q149">
+        <v>3.2</v>
+      </c>
+      <c r="R149">
+        <v>2.2</v>
+      </c>
+      <c r="S149">
+        <v>3.2</v>
+      </c>
+      <c r="T149">
+        <v>1.36</v>
+      </c>
+      <c r="U149">
+        <v>3</v>
+      </c>
+      <c r="V149">
+        <v>2.63</v>
+      </c>
+      <c r="W149">
+        <v>1.44</v>
+      </c>
+      <c r="X149">
+        <v>7</v>
+      </c>
+      <c r="Y149">
+        <v>1.1</v>
+      </c>
+      <c r="Z149">
+        <v>2.3</v>
+      </c>
+      <c r="AA149">
+        <v>3.3</v>
+      </c>
+      <c r="AB149">
+        <v>2.9</v>
+      </c>
+      <c r="AC149">
+        <v>1.05</v>
+      </c>
+      <c r="AD149">
+        <v>12</v>
+      </c>
+      <c r="AE149">
+        <v>1.26</v>
+      </c>
+      <c r="AF149">
+        <v>4</v>
+      </c>
+      <c r="AG149">
+        <v>1.84</v>
+      </c>
+      <c r="AH149">
+        <v>1.97</v>
+      </c>
+      <c r="AI149">
+        <v>1.62</v>
+      </c>
+      <c r="AJ149">
+        <v>2.2</v>
+      </c>
+      <c r="AK149">
+        <v>1.46</v>
+      </c>
+      <c r="AL149">
+        <v>1.3</v>
+      </c>
+      <c r="AM149">
+        <v>1.5</v>
+      </c>
+      <c r="AN149">
+        <v>1.13</v>
+      </c>
+      <c r="AO149">
+        <v>1.13</v>
+      </c>
+      <c r="AP149">
+        <v>1</v>
+      </c>
+      <c r="AQ149">
+        <v>1.33</v>
+      </c>
+      <c r="AR149">
+        <v>1.18</v>
+      </c>
+      <c r="AS149">
+        <v>1.42</v>
+      </c>
+      <c r="AT149">
+        <v>2.6</v>
+      </c>
+      <c r="AU149">
+        <v>5</v>
+      </c>
+      <c r="AV149">
+        <v>11</v>
+      </c>
+      <c r="AW149">
+        <v>8</v>
+      </c>
+      <c r="AX149">
+        <v>6</v>
+      </c>
+      <c r="AY149">
+        <v>15</v>
+      </c>
+      <c r="AZ149">
+        <v>20</v>
+      </c>
+      <c r="BA149">
+        <v>6</v>
+      </c>
+      <c r="BB149">
+        <v>3</v>
+      </c>
+      <c r="BC149">
+        <v>9</v>
+      </c>
+      <c r="BD149">
+        <v>1.78</v>
+      </c>
+      <c r="BE149">
+        <v>6.25</v>
+      </c>
+      <c r="BF149">
+        <v>2.28</v>
+      </c>
+      <c r="BG149">
+        <v>1.38</v>
+      </c>
+      <c r="BH149">
+        <v>2.75</v>
+      </c>
+      <c r="BI149">
+        <v>1.65</v>
+      </c>
+      <c r="BJ149">
+        <v>2.08</v>
+      </c>
+      <c r="BK149">
+        <v>2.05</v>
+      </c>
+      <c r="BL149">
+        <v>1.67</v>
+      </c>
+      <c r="BM149">
+        <v>2.65</v>
+      </c>
+      <c r="BN149">
+        <v>1.41</v>
+      </c>
+      <c r="BO149">
+        <v>3.45</v>
+      </c>
+      <c r="BP149">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="150" spans="1:68">
+      <c r="A150" s="1">
+        <v>149</v>
+      </c>
+      <c r="B150">
+        <v>7468508</v>
+      </c>
+      <c r="C150" t="s">
+        <v>68</v>
+      </c>
+      <c r="D150" t="s">
+        <v>69</v>
+      </c>
+      <c r="E150" s="2">
+        <v>45668.71180555555</v>
+      </c>
+      <c r="F150">
+        <v>17</v>
+      </c>
+      <c r="G150" t="s">
+        <v>78</v>
+      </c>
+      <c r="H150" t="s">
+        <v>87</v>
+      </c>
+      <c r="I150">
+        <v>1</v>
+      </c>
+      <c r="J150">
+        <v>1</v>
+      </c>
+      <c r="K150">
+        <v>2</v>
+      </c>
+      <c r="L150">
+        <v>1</v>
+      </c>
+      <c r="M150">
+        <v>2</v>
+      </c>
+      <c r="N150">
+        <v>3</v>
+      </c>
+      <c r="O150" t="s">
+        <v>195</v>
+      </c>
+      <c r="P150" t="s">
+        <v>279</v>
+      </c>
+      <c r="Q150">
+        <v>3.5</v>
+      </c>
+      <c r="R150">
+        <v>2.1</v>
+      </c>
+      <c r="S150">
+        <v>3.1</v>
+      </c>
+      <c r="T150">
+        <v>1.4</v>
+      </c>
+      <c r="U150">
+        <v>2.75</v>
+      </c>
+      <c r="V150">
+        <v>3</v>
+      </c>
+      <c r="W150">
+        <v>1.36</v>
+      </c>
+      <c r="X150">
+        <v>8</v>
+      </c>
+      <c r="Y150">
+        <v>1.08</v>
+      </c>
+      <c r="Z150">
+        <v>2.7</v>
+      </c>
+      <c r="AA150">
+        <v>3.25</v>
+      </c>
+      <c r="AB150">
+        <v>2.5</v>
+      </c>
+      <c r="AC150">
+        <v>1.06</v>
+      </c>
+      <c r="AD150">
+        <v>10</v>
+      </c>
+      <c r="AE150">
+        <v>1.32</v>
+      </c>
+      <c r="AF150">
+        <v>3.4</v>
+      </c>
+      <c r="AG150">
+        <v>1.92</v>
+      </c>
+      <c r="AH150">
+        <v>1.89</v>
+      </c>
+      <c r="AI150">
+        <v>1.7</v>
+      </c>
+      <c r="AJ150">
+        <v>2.05</v>
+      </c>
+      <c r="AK150">
+        <v>1.51</v>
+      </c>
+      <c r="AL150">
+        <v>1.31</v>
+      </c>
+      <c r="AM150">
+        <v>1.42</v>
+      </c>
+      <c r="AN150">
+        <v>2</v>
+      </c>
+      <c r="AO150">
+        <v>2.63</v>
+      </c>
+      <c r="AP150">
+        <v>1.78</v>
+      </c>
+      <c r="AQ150">
+        <v>2.67</v>
+      </c>
+      <c r="AR150">
+        <v>1.57</v>
+      </c>
+      <c r="AS150">
+        <v>1.32</v>
+      </c>
+      <c r="AT150">
+        <v>2.89</v>
+      </c>
+      <c r="AU150">
+        <v>4</v>
+      </c>
+      <c r="AV150">
+        <v>7</v>
+      </c>
+      <c r="AW150">
+        <v>2</v>
+      </c>
+      <c r="AX150">
+        <v>3</v>
+      </c>
+      <c r="AY150">
+        <v>7</v>
+      </c>
+      <c r="AZ150">
+        <v>12</v>
+      </c>
+      <c r="BA150">
+        <v>2</v>
+      </c>
+      <c r="BB150">
+        <v>3</v>
+      </c>
+      <c r="BC150">
+        <v>5</v>
+      </c>
+      <c r="BD150">
+        <v>1.74</v>
+      </c>
+      <c r="BE150">
+        <v>6.4</v>
+      </c>
+      <c r="BF150">
+        <v>2.33</v>
+      </c>
+      <c r="BG150">
+        <v>1.43</v>
+      </c>
+      <c r="BH150">
+        <v>2.55</v>
+      </c>
+      <c r="BI150">
+        <v>1.72</v>
+      </c>
+      <c r="BJ150">
+        <v>1.98</v>
+      </c>
+      <c r="BK150">
+        <v>2.17</v>
+      </c>
+      <c r="BL150">
+        <v>1.6</v>
+      </c>
+      <c r="BM150">
+        <v>2.8</v>
+      </c>
+      <c r="BN150">
+        <v>1.37</v>
+      </c>
+      <c r="BO150">
+        <v>3.7</v>
+      </c>
+      <c r="BP150">
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/France Ligue 1_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/France Ligue 1_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="962" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="986" uniqueCount="287">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -604,6 +604,18 @@
     <t>['43']</t>
   </si>
   <si>
+    <t>['8']</t>
+  </si>
+  <si>
+    <t>['61']</t>
+  </si>
+  <si>
+    <t>['35']</t>
+  </si>
+  <si>
+    <t>['13', '23']</t>
+  </si>
+  <si>
     <t>['3', '84', '86', '90']</t>
   </si>
   <si>
@@ -854,6 +866,15 @@
   </si>
   <si>
     <t>['45', '49']</t>
+  </si>
+  <si>
+    <t>['28', '77']</t>
+  </si>
+  <si>
+    <t>['30', '69', '90+9']</t>
+  </si>
+  <si>
+    <t>['14', '26']</t>
   </si>
 </sst>
 </file>
@@ -1215,7 +1236,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP150"/>
+  <dimension ref="A1:BP154"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1471,7 +1492,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="Q2">
         <v>6</v>
@@ -1549,7 +1570,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AQ2">
         <v>2.25</v>
@@ -1677,7 +1698,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="Q3">
         <v>3.4</v>
@@ -1883,7 +1904,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -2170,7 +2191,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ5">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2295,7 +2316,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="Q6">
         <v>3.75</v>
@@ -2501,7 +2522,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2579,10 +2600,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AQ7">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2785,7 +2806,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ8">
         <v>0.78</v>
@@ -2994,7 +3015,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ9">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3403,7 +3424,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AQ11">
         <v>0</v>
@@ -3531,7 +3552,7 @@
         <v>90</v>
       </c>
       <c r="P12" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="Q12">
         <v>2.8</v>
@@ -3818,7 +3839,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ13">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3943,7 +3964,7 @@
         <v>90</v>
       </c>
       <c r="P14" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="Q14">
         <v>2.65</v>
@@ -4355,7 +4376,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="Q16">
         <v>3.6</v>
@@ -4973,7 +4994,7 @@
         <v>101</v>
       </c>
       <c r="P19" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="Q19">
         <v>2.1</v>
@@ -5179,7 +5200,7 @@
         <v>102</v>
       </c>
       <c r="P20" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="Q20">
         <v>2.45</v>
@@ -5260,7 +5281,7 @@
         <v>2</v>
       </c>
       <c r="AQ20">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="AR20">
         <v>0.4</v>
@@ -5466,7 +5487,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ21">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="AR21">
         <v>1.56</v>
@@ -5591,7 +5612,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="Q22">
         <v>2.8</v>
@@ -5669,7 +5690,7 @@
         <v>1</v>
       </c>
       <c r="AP22">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AQ22">
         <v>0.78</v>
@@ -5797,7 +5818,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="Q23">
         <v>4.2</v>
@@ -5875,7 +5896,7 @@
         <v>3</v>
       </c>
       <c r="AP23">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ23">
         <v>2.67</v>
@@ -6003,7 +6024,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="Q24">
         <v>2.4</v>
@@ -6084,7 +6105,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ24">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR24">
         <v>1.57</v>
@@ -6209,7 +6230,7 @@
         <v>93</v>
       </c>
       <c r="P25" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="Q25">
         <v>4.5</v>
@@ -6493,7 +6514,7 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AQ26">
         <v>0.5</v>
@@ -6621,7 +6642,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="Q27">
         <v>3.4</v>
@@ -6827,7 +6848,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="Q28">
         <v>4.33</v>
@@ -7445,7 +7466,7 @@
         <v>90</v>
       </c>
       <c r="P31" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="Q31">
         <v>3.75</v>
@@ -7729,7 +7750,7 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AQ32">
         <v>0.38</v>
@@ -8063,7 +8084,7 @@
         <v>114</v>
       </c>
       <c r="P34" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="Q34">
         <v>2.3</v>
@@ -8144,7 +8165,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ34">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR34">
         <v>1.25</v>
@@ -8269,7 +8290,7 @@
         <v>91</v>
       </c>
       <c r="P35" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -8553,7 +8574,7 @@
         <v>3</v>
       </c>
       <c r="AP36">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ36">
         <v>0.75</v>
@@ -8968,7 +8989,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ38">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="AR38">
         <v>1.16</v>
@@ -9093,7 +9114,7 @@
         <v>117</v>
       </c>
       <c r="P39" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="Q39">
         <v>2.2</v>
@@ -9174,7 +9195,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ39">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="AR39">
         <v>1.47</v>
@@ -9299,7 +9320,7 @@
         <v>118</v>
       </c>
       <c r="P40" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9380,7 +9401,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ40">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR40">
         <v>1.95</v>
@@ -9505,7 +9526,7 @@
         <v>119</v>
       </c>
       <c r="P41" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="Q41">
         <v>6</v>
@@ -10123,7 +10144,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="Q44">
         <v>3.75</v>
@@ -10329,7 +10350,7 @@
         <v>122</v>
       </c>
       <c r="P45" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="Q45">
         <v>2.88</v>
@@ -10407,7 +10428,7 @@
         <v>0</v>
       </c>
       <c r="AP45">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AQ45">
         <v>0.5</v>
@@ -10535,7 +10556,7 @@
         <v>123</v>
       </c>
       <c r="P46" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="Q46">
         <v>3.25</v>
@@ -10947,7 +10968,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="Q48">
         <v>1.83</v>
@@ -11025,7 +11046,7 @@
         <v>0</v>
       </c>
       <c r="AP48">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AQ48">
         <v>0.13</v>
@@ -11359,7 +11380,7 @@
         <v>90</v>
       </c>
       <c r="P50" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="Q50">
         <v>5</v>
@@ -11437,7 +11458,7 @@
         <v>1.5</v>
       </c>
       <c r="AP50">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AQ50">
         <v>1.56</v>
@@ -11565,7 +11586,7 @@
         <v>126</v>
       </c>
       <c r="P51" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="Q51">
         <v>1.8</v>
@@ -11771,7 +11792,7 @@
         <v>127</v>
       </c>
       <c r="P52" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="Q52">
         <v>3.1</v>
@@ -11849,7 +11870,7 @@
         <v>0.5</v>
       </c>
       <c r="AP52">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ52">
         <v>1.33</v>
@@ -11977,7 +11998,7 @@
         <v>128</v>
       </c>
       <c r="P53" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="Q53">
         <v>2.3</v>
@@ -12058,7 +12079,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ53">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="AR53">
         <v>1.5</v>
@@ -12183,7 +12204,7 @@
         <v>106</v>
       </c>
       <c r="P54" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="Q54">
         <v>4</v>
@@ -12676,7 +12697,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ56">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR56">
         <v>1.67</v>
@@ -12801,7 +12822,7 @@
         <v>131</v>
       </c>
       <c r="P57" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="Q57">
         <v>3.25</v>
@@ -13213,7 +13234,7 @@
         <v>133</v>
       </c>
       <c r="P59" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="Q59">
         <v>3.2</v>
@@ -13831,7 +13852,7 @@
         <v>136</v>
       </c>
       <c r="P62" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="Q62">
         <v>3.4</v>
@@ -13912,7 +13933,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ62">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR62">
         <v>1.38</v>
@@ -14037,7 +14058,7 @@
         <v>137</v>
       </c>
       <c r="P63" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="Q63">
         <v>2.38</v>
@@ -14243,7 +14264,7 @@
         <v>138</v>
       </c>
       <c r="P64" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="Q64">
         <v>4.75</v>
@@ -14655,7 +14676,7 @@
         <v>139</v>
       </c>
       <c r="P66" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="Q66">
         <v>3.4</v>
@@ -14861,7 +14882,7 @@
         <v>90</v>
       </c>
       <c r="P67" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="Q67">
         <v>5.5</v>
@@ -14942,7 +14963,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ67">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR67">
         <v>1.42</v>
@@ -15067,7 +15088,7 @@
         <v>140</v>
       </c>
       <c r="P68" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="Q68">
         <v>1.73</v>
@@ -15145,10 +15166,10 @@
         <v>0.67</v>
       </c>
       <c r="AP68">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AQ68">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="AR68">
         <v>2.38</v>
@@ -15273,7 +15294,7 @@
         <v>90</v>
       </c>
       <c r="P69" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="Q69">
         <v>4</v>
@@ -15351,7 +15372,7 @@
         <v>1.33</v>
       </c>
       <c r="AP69">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AQ69">
         <v>1.33</v>
@@ -15479,7 +15500,7 @@
         <v>141</v>
       </c>
       <c r="P70" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q70">
         <v>2.1</v>
@@ -15557,10 +15578,10 @@
         <v>0.67</v>
       </c>
       <c r="AP70">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ70">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR70">
         <v>1.25</v>
@@ -15685,7 +15706,7 @@
         <v>93</v>
       </c>
       <c r="P71" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="Q71">
         <v>3.6</v>
@@ -15891,7 +15912,7 @@
         <v>142</v>
       </c>
       <c r="P72" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="Q72">
         <v>3.1</v>
@@ -16097,7 +16118,7 @@
         <v>90</v>
       </c>
       <c r="P73" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="Q73">
         <v>4.33</v>
@@ -16175,7 +16196,7 @@
         <v>2.25</v>
       </c>
       <c r="AP73">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AQ73">
         <v>2.67</v>
@@ -16509,7 +16530,7 @@
         <v>143</v>
       </c>
       <c r="P75" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="Q75">
         <v>3</v>
@@ -16590,7 +16611,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ75">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="AR75">
         <v>1.25</v>
@@ -16715,7 +16736,7 @@
         <v>144</v>
       </c>
       <c r="P76" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -16921,7 +16942,7 @@
         <v>90</v>
       </c>
       <c r="P77" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17127,7 +17148,7 @@
         <v>145</v>
       </c>
       <c r="P78" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="Q78">
         <v>2.1</v>
@@ -17333,7 +17354,7 @@
         <v>90</v>
       </c>
       <c r="P79" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="Q79">
         <v>3.5</v>
@@ -17411,7 +17432,7 @@
         <v>0.33</v>
       </c>
       <c r="AP79">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AQ79">
         <v>1.25</v>
@@ -17539,7 +17560,7 @@
         <v>146</v>
       </c>
       <c r="P80" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="Q80">
         <v>2.63</v>
@@ -17951,7 +17972,7 @@
         <v>90</v>
       </c>
       <c r="P82" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="Q82">
         <v>3.6</v>
@@ -18238,7 +18259,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ83">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR83">
         <v>1.55</v>
@@ -18647,10 +18668,10 @@
         <v>1.8</v>
       </c>
       <c r="AP85">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AQ85">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR85">
         <v>2.29</v>
@@ -18775,7 +18796,7 @@
         <v>90</v>
       </c>
       <c r="P86" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="Q86">
         <v>3.2</v>
@@ -19062,7 +19083,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ87">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="AR87">
         <v>1.3</v>
@@ -19265,7 +19286,7 @@
         <v>1.75</v>
       </c>
       <c r="AP88">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ88">
         <v>1.38</v>
@@ -19677,7 +19698,7 @@
         <v>0</v>
       </c>
       <c r="AP90">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AQ90">
         <v>0</v>
@@ -19805,7 +19826,7 @@
         <v>153</v>
       </c>
       <c r="P91" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="Q91">
         <v>4.33</v>
@@ -20011,7 +20032,7 @@
         <v>154</v>
       </c>
       <c r="P92" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="Q92">
         <v>1.91</v>
@@ -20217,7 +20238,7 @@
         <v>144</v>
       </c>
       <c r="P93" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -20423,7 +20444,7 @@
         <v>155</v>
       </c>
       <c r="P94" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -20629,7 +20650,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="Q95">
         <v>8.5</v>
@@ -20835,7 +20856,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="Q96">
         <v>3.2</v>
@@ -21041,7 +21062,7 @@
         <v>90</v>
       </c>
       <c r="P97" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="Q97">
         <v>2.88</v>
@@ -21247,7 +21268,7 @@
         <v>158</v>
       </c>
       <c r="P98" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="Q98">
         <v>3.5</v>
@@ -21325,7 +21346,7 @@
         <v>0.75</v>
       </c>
       <c r="AP98">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AQ98">
         <v>0.38</v>
@@ -21453,7 +21474,7 @@
         <v>90</v>
       </c>
       <c r="P99" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="Q99">
         <v>3.75</v>
@@ -21531,7 +21552,7 @@
         <v>1.4</v>
       </c>
       <c r="AP99">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AQ99">
         <v>1.38</v>
@@ -21740,7 +21761,7 @@
         <v>2</v>
       </c>
       <c r="AQ100">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="AR100">
         <v>1.78</v>
@@ -21865,7 +21886,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="Q101">
         <v>2.05</v>
@@ -22149,7 +22170,7 @@
         <v>1.4</v>
       </c>
       <c r="AP102">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AQ102">
         <v>1.25</v>
@@ -22277,7 +22298,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -23182,7 +23203,7 @@
         <v>2</v>
       </c>
       <c r="AQ107">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR107">
         <v>1.49</v>
@@ -23307,7 +23328,7 @@
         <v>90</v>
       </c>
       <c r="P108" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="Q108">
         <v>2.6</v>
@@ -23513,7 +23534,7 @@
         <v>166</v>
       </c>
       <c r="P109" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="Q109">
         <v>2.38</v>
@@ -23594,7 +23615,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ109">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="AR109">
         <v>1.61</v>
@@ -23719,7 +23740,7 @@
         <v>90</v>
       </c>
       <c r="P110" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="Q110">
         <v>3.4</v>
@@ -23800,7 +23821,7 @@
         <v>1</v>
       </c>
       <c r="AQ110">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR110">
         <v>1.22</v>
@@ -24006,7 +24027,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ111">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="AR111">
         <v>1.53</v>
@@ -24131,7 +24152,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="Q112">
         <v>2.88</v>
@@ -24212,7 +24233,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ112">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="AR112">
         <v>1.45</v>
@@ -24415,7 +24436,7 @@
         <v>0.83</v>
       </c>
       <c r="AP113">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AQ113">
         <v>0.78</v>
@@ -24543,7 +24564,7 @@
         <v>170</v>
       </c>
       <c r="P114" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="Q114">
         <v>4.33</v>
@@ -24621,7 +24642,7 @@
         <v>1.83</v>
       </c>
       <c r="AP114">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AQ114">
         <v>1.56</v>
@@ -24749,7 +24770,7 @@
         <v>90</v>
       </c>
       <c r="P115" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="Q115">
         <v>3</v>
@@ -24827,10 +24848,10 @@
         <v>1</v>
       </c>
       <c r="AP115">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AQ115">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR115">
         <v>1.18</v>
@@ -25033,7 +25054,7 @@
         <v>0.67</v>
       </c>
       <c r="AP116">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ116">
         <v>0.5</v>
@@ -25161,7 +25182,7 @@
         <v>172</v>
       </c>
       <c r="P117" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="Q117">
         <v>2.6</v>
@@ -25367,7 +25388,7 @@
         <v>173</v>
       </c>
       <c r="P118" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="Q118">
         <v>3.1</v>
@@ -26191,7 +26212,7 @@
         <v>176</v>
       </c>
       <c r="P122" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="Q122">
         <v>2.05</v>
@@ -26397,7 +26418,7 @@
         <v>90</v>
       </c>
       <c r="P123" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="Q123">
         <v>4.75</v>
@@ -27221,7 +27242,7 @@
         <v>90</v>
       </c>
       <c r="P127" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q127">
         <v>5</v>
@@ -27505,10 +27526,10 @@
         <v>0.14</v>
       </c>
       <c r="AP128">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AQ128">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="AR128">
         <v>1.4</v>
@@ -27633,7 +27654,7 @@
         <v>148</v>
       </c>
       <c r="P129" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="Q129">
         <v>2.88</v>
@@ -27839,7 +27860,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="Q130">
         <v>4.33</v>
@@ -27920,7 +27941,7 @@
         <v>2</v>
       </c>
       <c r="AQ130">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR130">
         <v>1.37</v>
@@ -28251,7 +28272,7 @@
         <v>181</v>
       </c>
       <c r="P132" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="Q132">
         <v>3.5</v>
@@ -28329,7 +28350,7 @@
         <v>1.14</v>
       </c>
       <c r="AP132">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AQ132">
         <v>1.33</v>
@@ -28457,7 +28478,7 @@
         <v>90</v>
       </c>
       <c r="P133" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="Q133">
         <v>3.5</v>
@@ -28535,10 +28556,10 @@
         <v>0.29</v>
       </c>
       <c r="AP133">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AQ133">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="AR133">
         <v>1.14</v>
@@ -28950,7 +28971,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ135">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AR135">
         <v>1.64</v>
@@ -29153,7 +29174,7 @@
         <v>1.71</v>
       </c>
       <c r="AP136">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AQ136">
         <v>1.33</v>
@@ -29281,7 +29302,7 @@
         <v>185</v>
       </c>
       <c r="P137" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="Q137">
         <v>3.4</v>
@@ -29487,7 +29508,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="Q138">
         <v>2.88</v>
@@ -29693,7 +29714,7 @@
         <v>187</v>
       </c>
       <c r="P139" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="Q139">
         <v>4</v>
@@ -29899,7 +29920,7 @@
         <v>129</v>
       </c>
       <c r="P140" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="Q140">
         <v>2.2</v>
@@ -30929,7 +30950,7 @@
         <v>191</v>
       </c>
       <c r="P145" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="Q145">
         <v>1.8</v>
@@ -31135,7 +31156,7 @@
         <v>192</v>
       </c>
       <c r="P146" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="Q146">
         <v>4.33</v>
@@ -31234,16 +31255,16 @@
         <v>8</v>
       </c>
       <c r="AW146">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AX146">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AY146">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ146">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="BA146">
         <v>3</v>
@@ -31547,7 +31568,7 @@
         <v>193</v>
       </c>
       <c r="P148" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="Q148">
         <v>3.6</v>
@@ -31643,19 +31664,19 @@
         <v>7</v>
       </c>
       <c r="AV148">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW148">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AX148">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY148">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ148">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA148">
         <v>4</v>
@@ -31753,7 +31774,7 @@
         <v>194</v>
       </c>
       <c r="P149" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="Q149">
         <v>3.2</v>
@@ -31846,7 +31867,7 @@
         <v>2.6</v>
       </c>
       <c r="AU149">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV149">
         <v>11</v>
@@ -31855,13 +31876,13 @@
         <v>8</v>
       </c>
       <c r="AX149">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AY149">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ149">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="BA149">
         <v>6</v>
@@ -31959,7 +31980,7 @@
         <v>195</v>
       </c>
       <c r="P150" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="Q150">
         <v>3.5</v>
@@ -32052,22 +32073,22 @@
         <v>2.89</v>
       </c>
       <c r="AU150">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV150">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW150">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX150">
         <v>3</v>
       </c>
       <c r="AY150">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ150">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BA150">
         <v>2</v>
@@ -32116,6 +32137,830 @@
       </c>
       <c r="BP150">
         <v>1.22</v>
+      </c>
+    </row>
+    <row r="151" spans="1:68">
+      <c r="A151" s="1">
+        <v>150</v>
+      </c>
+      <c r="B151">
+        <v>7468504</v>
+      </c>
+      <c r="C151" t="s">
+        <v>68</v>
+      </c>
+      <c r="D151" t="s">
+        <v>69</v>
+      </c>
+      <c r="E151" s="2">
+        <v>45669.45833333334</v>
+      </c>
+      <c r="F151">
+        <v>17</v>
+      </c>
+      <c r="G151" t="s">
+        <v>70</v>
+      </c>
+      <c r="H151" t="s">
+        <v>83</v>
+      </c>
+      <c r="I151">
+        <v>1</v>
+      </c>
+      <c r="J151">
+        <v>1</v>
+      </c>
+      <c r="K151">
+        <v>2</v>
+      </c>
+      <c r="L151">
+        <v>1</v>
+      </c>
+      <c r="M151">
+        <v>2</v>
+      </c>
+      <c r="N151">
+        <v>3</v>
+      </c>
+      <c r="O151" t="s">
+        <v>196</v>
+      </c>
+      <c r="P151" t="s">
+        <v>284</v>
+      </c>
+      <c r="Q151">
+        <v>5.25</v>
+      </c>
+      <c r="R151">
+        <v>2.1</v>
+      </c>
+      <c r="S151">
+        <v>2.2</v>
+      </c>
+      <c r="T151">
+        <v>1.41</v>
+      </c>
+      <c r="U151">
+        <v>2.65</v>
+      </c>
+      <c r="V151">
+        <v>2.8</v>
+      </c>
+      <c r="W151">
+        <v>1.38</v>
+      </c>
+      <c r="X151">
+        <v>7.25</v>
+      </c>
+      <c r="Y151">
+        <v>1.08</v>
+      </c>
+      <c r="Z151">
+        <v>5</v>
+      </c>
+      <c r="AA151">
+        <v>3.65</v>
+      </c>
+      <c r="AB151">
+        <v>1.67</v>
+      </c>
+      <c r="AC151">
+        <v>1.06</v>
+      </c>
+      <c r="AD151">
+        <v>10</v>
+      </c>
+      <c r="AE151">
+        <v>1.33</v>
+      </c>
+      <c r="AF151">
+        <v>3.4</v>
+      </c>
+      <c r="AG151">
+        <v>2</v>
+      </c>
+      <c r="AH151">
+        <v>1.8</v>
+      </c>
+      <c r="AI151">
+        <v>1.93</v>
+      </c>
+      <c r="AJ151">
+        <v>1.75</v>
+      </c>
+      <c r="AK151">
+        <v>2.15</v>
+      </c>
+      <c r="AL151">
+        <v>1.26</v>
+      </c>
+      <c r="AM151">
+        <v>1.15</v>
+      </c>
+      <c r="AN151">
+        <v>0.75</v>
+      </c>
+      <c r="AO151">
+        <v>1.63</v>
+      </c>
+      <c r="AP151">
+        <v>0.67</v>
+      </c>
+      <c r="AQ151">
+        <v>1.78</v>
+      </c>
+      <c r="AR151">
+        <v>1.15</v>
+      </c>
+      <c r="AS151">
+        <v>1.32</v>
+      </c>
+      <c r="AT151">
+        <v>2.47</v>
+      </c>
+      <c r="AU151">
+        <v>5</v>
+      </c>
+      <c r="AV151">
+        <v>8</v>
+      </c>
+      <c r="AW151">
+        <v>1</v>
+      </c>
+      <c r="AX151">
+        <v>10</v>
+      </c>
+      <c r="AY151">
+        <v>9</v>
+      </c>
+      <c r="AZ151">
+        <v>26</v>
+      </c>
+      <c r="BA151">
+        <v>3</v>
+      </c>
+      <c r="BB151">
+        <v>8</v>
+      </c>
+      <c r="BC151">
+        <v>11</v>
+      </c>
+      <c r="BD151">
+        <v>3.05</v>
+      </c>
+      <c r="BE151">
+        <v>6.75</v>
+      </c>
+      <c r="BF151">
+        <v>1.47</v>
+      </c>
+      <c r="BG151">
+        <v>1.44</v>
+      </c>
+      <c r="BH151">
+        <v>2.55</v>
+      </c>
+      <c r="BI151">
+        <v>1.76</v>
+      </c>
+      <c r="BJ151">
+        <v>1.94</v>
+      </c>
+      <c r="BK151">
+        <v>2.2</v>
+      </c>
+      <c r="BL151">
+        <v>1.58</v>
+      </c>
+      <c r="BM151">
+        <v>2.9</v>
+      </c>
+      <c r="BN151">
+        <v>1.35</v>
+      </c>
+      <c r="BO151">
+        <v>3.8</v>
+      </c>
+      <c r="BP151">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="152" spans="1:68">
+      <c r="A152" s="1">
+        <v>151</v>
+      </c>
+      <c r="B152">
+        <v>7468505</v>
+      </c>
+      <c r="C152" t="s">
+        <v>68</v>
+      </c>
+      <c r="D152" t="s">
+        <v>69</v>
+      </c>
+      <c r="E152" s="2">
+        <v>45669.55208333334</v>
+      </c>
+      <c r="F152">
+        <v>17</v>
+      </c>
+      <c r="G152" t="s">
+        <v>75</v>
+      </c>
+      <c r="H152" t="s">
+        <v>77</v>
+      </c>
+      <c r="I152">
+        <v>0</v>
+      </c>
+      <c r="J152">
+        <v>1</v>
+      </c>
+      <c r="K152">
+        <v>1</v>
+      </c>
+      <c r="L152">
+        <v>1</v>
+      </c>
+      <c r="M152">
+        <v>3</v>
+      </c>
+      <c r="N152">
+        <v>4</v>
+      </c>
+      <c r="O152" t="s">
+        <v>197</v>
+      </c>
+      <c r="P152" t="s">
+        <v>285</v>
+      </c>
+      <c r="Q152">
+        <v>2.6</v>
+      </c>
+      <c r="R152">
+        <v>2.1</v>
+      </c>
+      <c r="S152">
+        <v>3.75</v>
+      </c>
+      <c r="T152">
+        <v>1.37</v>
+      </c>
+      <c r="U152">
+        <v>2.85</v>
+      </c>
+      <c r="V152">
+        <v>2.65</v>
+      </c>
+      <c r="W152">
+        <v>1.41</v>
+      </c>
+      <c r="X152">
+        <v>6.75</v>
+      </c>
+      <c r="Y152">
+        <v>1.09</v>
+      </c>
+      <c r="Z152">
+        <v>2</v>
+      </c>
+      <c r="AA152">
+        <v>3.5</v>
+      </c>
+      <c r="AB152">
+        <v>3.5</v>
+      </c>
+      <c r="AC152">
+        <v>1.05</v>
+      </c>
+      <c r="AD152">
+        <v>11</v>
+      </c>
+      <c r="AE152">
+        <v>1.3</v>
+      </c>
+      <c r="AF152">
+        <v>3.6</v>
+      </c>
+      <c r="AG152">
+        <v>1.73</v>
+      </c>
+      <c r="AH152">
+        <v>2.05</v>
+      </c>
+      <c r="AI152">
+        <v>1.71</v>
+      </c>
+      <c r="AJ152">
+        <v>1.98</v>
+      </c>
+      <c r="AK152">
+        <v>1.3</v>
+      </c>
+      <c r="AL152">
+        <v>1.29</v>
+      </c>
+      <c r="AM152">
+        <v>1.71</v>
+      </c>
+      <c r="AN152">
+        <v>1.13</v>
+      </c>
+      <c r="AO152">
+        <v>1.13</v>
+      </c>
+      <c r="AP152">
+        <v>1</v>
+      </c>
+      <c r="AQ152">
+        <v>1.33</v>
+      </c>
+      <c r="AR152">
+        <v>1.44</v>
+      </c>
+      <c r="AS152">
+        <v>0.96</v>
+      </c>
+      <c r="AT152">
+        <v>2.4</v>
+      </c>
+      <c r="AU152">
+        <v>4</v>
+      </c>
+      <c r="AV152">
+        <v>10</v>
+      </c>
+      <c r="AW152">
+        <v>7</v>
+      </c>
+      <c r="AX152">
+        <v>13</v>
+      </c>
+      <c r="AY152">
+        <v>13</v>
+      </c>
+      <c r="AZ152">
+        <v>27</v>
+      </c>
+      <c r="BA152">
+        <v>3</v>
+      </c>
+      <c r="BB152">
+        <v>3</v>
+      </c>
+      <c r="BC152">
+        <v>6</v>
+      </c>
+      <c r="BD152">
+        <v>1.6</v>
+      </c>
+      <c r="BE152">
+        <v>6.75</v>
+      </c>
+      <c r="BF152">
+        <v>2.55</v>
+      </c>
+      <c r="BG152">
+        <v>1.33</v>
+      </c>
+      <c r="BH152">
+        <v>2.95</v>
+      </c>
+      <c r="BI152">
+        <v>1.56</v>
+      </c>
+      <c r="BJ152">
+        <v>2.23</v>
+      </c>
+      <c r="BK152">
+        <v>1.92</v>
+      </c>
+      <c r="BL152">
+        <v>1.77</v>
+      </c>
+      <c r="BM152">
+        <v>2.43</v>
+      </c>
+      <c r="BN152">
+        <v>1.47</v>
+      </c>
+      <c r="BO152">
+        <v>3.15</v>
+      </c>
+      <c r="BP152">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="153" spans="1:68">
+      <c r="A153" s="1">
+        <v>152</v>
+      </c>
+      <c r="B153">
+        <v>7468500</v>
+      </c>
+      <c r="C153" t="s">
+        <v>68</v>
+      </c>
+      <c r="D153" t="s">
+        <v>69</v>
+      </c>
+      <c r="E153" s="2">
+        <v>45669.55208333334</v>
+      </c>
+      <c r="F153">
+        <v>17</v>
+      </c>
+      <c r="G153" t="s">
+        <v>76</v>
+      </c>
+      <c r="H153" t="s">
+        <v>84</v>
+      </c>
+      <c r="I153">
+        <v>1</v>
+      </c>
+      <c r="J153">
+        <v>2</v>
+      </c>
+      <c r="K153">
+        <v>3</v>
+      </c>
+      <c r="L153">
+        <v>1</v>
+      </c>
+      <c r="M153">
+        <v>2</v>
+      </c>
+      <c r="N153">
+        <v>3</v>
+      </c>
+      <c r="O153" t="s">
+        <v>198</v>
+      </c>
+      <c r="P153" t="s">
+        <v>286</v>
+      </c>
+      <c r="Q153">
+        <v>2.3</v>
+      </c>
+      <c r="R153">
+        <v>2.2</v>
+      </c>
+      <c r="S153">
+        <v>4.33</v>
+      </c>
+      <c r="T153">
+        <v>1.34</v>
+      </c>
+      <c r="U153">
+        <v>2.95</v>
+      </c>
+      <c r="V153">
+        <v>2.55</v>
+      </c>
+      <c r="W153">
+        <v>1.46</v>
+      </c>
+      <c r="X153">
+        <v>6.25</v>
+      </c>
+      <c r="Y153">
+        <v>1.1</v>
+      </c>
+      <c r="Z153">
+        <v>1.73</v>
+      </c>
+      <c r="AA153">
+        <v>3.8</v>
+      </c>
+      <c r="AB153">
+        <v>4.33</v>
+      </c>
+      <c r="AC153">
+        <v>1.04</v>
+      </c>
+      <c r="AD153">
+        <v>13</v>
+      </c>
+      <c r="AE153">
+        <v>1.26</v>
+      </c>
+      <c r="AF153">
+        <v>4</v>
+      </c>
+      <c r="AG153">
+        <v>1.73</v>
+      </c>
+      <c r="AH153">
+        <v>2.05</v>
+      </c>
+      <c r="AI153">
+        <v>1.72</v>
+      </c>
+      <c r="AJ153">
+        <v>1.98</v>
+      </c>
+      <c r="AK153">
+        <v>1.21</v>
+      </c>
+      <c r="AL153">
+        <v>1.26</v>
+      </c>
+      <c r="AM153">
+        <v>1.98</v>
+      </c>
+      <c r="AN153">
+        <v>1.75</v>
+      </c>
+      <c r="AO153">
+        <v>0.63</v>
+      </c>
+      <c r="AP153">
+        <v>1.56</v>
+      </c>
+      <c r="AQ153">
+        <v>0.89</v>
+      </c>
+      <c r="AR153">
+        <v>1.39</v>
+      </c>
+      <c r="AS153">
+        <v>1.33</v>
+      </c>
+      <c r="AT153">
+        <v>2.72</v>
+      </c>
+      <c r="AU153">
+        <v>7</v>
+      </c>
+      <c r="AV153">
+        <v>4</v>
+      </c>
+      <c r="AW153">
+        <v>13</v>
+      </c>
+      <c r="AX153">
+        <v>5</v>
+      </c>
+      <c r="AY153">
+        <v>26</v>
+      </c>
+      <c r="AZ153">
+        <v>10</v>
+      </c>
+      <c r="BA153">
+        <v>3</v>
+      </c>
+      <c r="BB153">
+        <v>2</v>
+      </c>
+      <c r="BC153">
+        <v>5</v>
+      </c>
+      <c r="BD153">
+        <v>1.48</v>
+      </c>
+      <c r="BE153">
+        <v>6.5</v>
+      </c>
+      <c r="BF153">
+        <v>3.05</v>
+      </c>
+      <c r="BG153">
+        <v>1.37</v>
+      </c>
+      <c r="BH153">
+        <v>2.8</v>
+      </c>
+      <c r="BI153">
+        <v>1.63</v>
+      </c>
+      <c r="BJ153">
+        <v>2.12</v>
+      </c>
+      <c r="BK153">
+        <v>2</v>
+      </c>
+      <c r="BL153">
+        <v>1.71</v>
+      </c>
+      <c r="BM153">
+        <v>2.55</v>
+      </c>
+      <c r="BN153">
+        <v>1.44</v>
+      </c>
+      <c r="BO153">
+        <v>3.4</v>
+      </c>
+      <c r="BP153">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="154" spans="1:68">
+      <c r="A154" s="1">
+        <v>153</v>
+      </c>
+      <c r="B154">
+        <v>7468507</v>
+      </c>
+      <c r="C154" t="s">
+        <v>68</v>
+      </c>
+      <c r="D154" t="s">
+        <v>69</v>
+      </c>
+      <c r="E154" s="2">
+        <v>45669.69791666666</v>
+      </c>
+      <c r="F154">
+        <v>17</v>
+      </c>
+      <c r="G154" t="s">
+        <v>79</v>
+      </c>
+      <c r="H154" t="s">
+        <v>82</v>
+      </c>
+      <c r="I154">
+        <v>2</v>
+      </c>
+      <c r="J154">
+        <v>0</v>
+      </c>
+      <c r="K154">
+        <v>2</v>
+      </c>
+      <c r="L154">
+        <v>2</v>
+      </c>
+      <c r="M154">
+        <v>1</v>
+      </c>
+      <c r="N154">
+        <v>3</v>
+      </c>
+      <c r="O154" t="s">
+        <v>199</v>
+      </c>
+      <c r="P154" t="s">
+        <v>141</v>
+      </c>
+      <c r="Q154">
+        <v>1.35</v>
+      </c>
+      <c r="R154">
+        <v>3.7</v>
+      </c>
+      <c r="S154">
+        <v>10.5</v>
+      </c>
+      <c r="T154">
+        <v>1.14</v>
+      </c>
+      <c r="U154">
+        <v>5.25</v>
+      </c>
+      <c r="V154">
+        <v>1.66</v>
+      </c>
+      <c r="W154">
+        <v>2.05</v>
+      </c>
+      <c r="X154">
+        <v>3.1</v>
+      </c>
+      <c r="Y154">
+        <v>1.32</v>
+      </c>
+      <c r="Z154">
+        <v>1.06</v>
+      </c>
+      <c r="AA154">
+        <v>12</v>
+      </c>
+      <c r="AB154">
+        <v>21</v>
+      </c>
+      <c r="AC154">
+        <v>1.01</v>
+      </c>
+      <c r="AD154">
+        <v>14</v>
+      </c>
+      <c r="AE154">
+        <v>1.05</v>
+      </c>
+      <c r="AF154">
+        <v>10</v>
+      </c>
+      <c r="AG154">
+        <v>1.22</v>
+      </c>
+      <c r="AH154">
+        <v>4.2</v>
+      </c>
+      <c r="AI154">
+        <v>2</v>
+      </c>
+      <c r="AJ154">
+        <v>1.7</v>
+      </c>
+      <c r="AK154">
+        <v>1.01</v>
+      </c>
+      <c r="AL154">
+        <v>1.04</v>
+      </c>
+      <c r="AM154">
+        <v>7.25</v>
+      </c>
+      <c r="AN154">
+        <v>2.75</v>
+      </c>
+      <c r="AO154">
+        <v>0.13</v>
+      </c>
+      <c r="AP154">
+        <v>2.78</v>
+      </c>
+      <c r="AQ154">
+        <v>0.11</v>
+      </c>
+      <c r="AR154">
+        <v>2.26</v>
+      </c>
+      <c r="AS154">
+        <v>0.98</v>
+      </c>
+      <c r="AT154">
+        <v>3.24</v>
+      </c>
+      <c r="AU154">
+        <v>10</v>
+      </c>
+      <c r="AV154">
+        <v>4</v>
+      </c>
+      <c r="AW154">
+        <v>16</v>
+      </c>
+      <c r="AX154">
+        <v>4</v>
+      </c>
+      <c r="AY154">
+        <v>28</v>
+      </c>
+      <c r="AZ154">
+        <v>11</v>
+      </c>
+      <c r="BA154">
+        <v>7</v>
+      </c>
+      <c r="BB154">
+        <v>3</v>
+      </c>
+      <c r="BC154">
+        <v>10</v>
+      </c>
+      <c r="BD154">
+        <v>1.05</v>
+      </c>
+      <c r="BE154">
+        <v>13</v>
+      </c>
+      <c r="BF154">
+        <v>10.5</v>
+      </c>
+      <c r="BG154">
+        <v>1.25</v>
+      </c>
+      <c r="BH154">
+        <v>3.45</v>
+      </c>
+      <c r="BI154">
+        <v>1.43</v>
+      </c>
+      <c r="BJ154">
+        <v>2.55</v>
+      </c>
+      <c r="BK154">
+        <v>1.71</v>
+      </c>
+      <c r="BL154">
+        <v>2</v>
+      </c>
+      <c r="BM154">
+        <v>2.08</v>
+      </c>
+      <c r="BN154">
+        <v>1.65</v>
+      </c>
+      <c r="BO154">
+        <v>2.65</v>
+      </c>
+      <c r="BP154">
+        <v>1.41</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/France Ligue 1_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/France Ligue 1_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="986" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1016" uniqueCount="294">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -616,6 +616,18 @@
     <t>['13', '23']</t>
   </si>
   <si>
+    <t>['54', '82']</t>
+  </si>
+  <si>
+    <t>['48', '63']</t>
+  </si>
+  <si>
+    <t>['36']</t>
+  </si>
+  <si>
+    <t>['77']</t>
+  </si>
+  <si>
     <t>['3', '84', '86', '90']</t>
   </si>
   <si>
@@ -875,6 +887,15 @@
   </si>
   <si>
     <t>['14', '26']</t>
+  </si>
+  <si>
+    <t>['32']</t>
+  </si>
+  <si>
+    <t>['59', '86']</t>
+  </si>
+  <si>
+    <t>['27', '73']</t>
   </si>
 </sst>
 </file>
@@ -1236,7 +1257,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP154"/>
+  <dimension ref="A1:BP159"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1492,7 +1513,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="Q2">
         <v>6</v>
@@ -1573,7 +1594,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ2">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1698,7 +1719,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="Q3">
         <v>3.4</v>
@@ -1904,7 +1925,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -2316,7 +2337,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="Q6">
         <v>3.75</v>
@@ -2397,7 +2418,7 @@
         <v>2</v>
       </c>
       <c r="AQ6">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2522,7 +2543,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2600,7 +2621,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ7">
         <v>0.89</v>
@@ -3218,7 +3239,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ10">
         <v>1.33</v>
@@ -3552,7 +3573,7 @@
         <v>90</v>
       </c>
       <c r="P12" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="Q12">
         <v>2.8</v>
@@ -3630,10 +3651,10 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AQ12">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3836,7 +3857,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AQ13">
         <v>1.33</v>
@@ -3964,7 +3985,7 @@
         <v>90</v>
       </c>
       <c r="P14" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="Q14">
         <v>2.65</v>
@@ -4248,10 +4269,10 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AQ15">
-        <v>0.38</v>
+        <v>0.67</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4376,7 +4397,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="Q16">
         <v>3.6</v>
@@ -4869,7 +4890,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ18">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -4994,7 +5015,7 @@
         <v>101</v>
       </c>
       <c r="P19" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="Q19">
         <v>2.1</v>
@@ -5200,7 +5221,7 @@
         <v>102</v>
       </c>
       <c r="P20" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="Q20">
         <v>2.45</v>
@@ -5278,7 +5299,7 @@
         <v>1</v>
       </c>
       <c r="AP20">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AQ20">
         <v>0.89</v>
@@ -5612,7 +5633,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="Q22">
         <v>2.8</v>
@@ -5690,7 +5711,7 @@
         <v>1</v>
       </c>
       <c r="AP22">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ22">
         <v>0.78</v>
@@ -5818,7 +5839,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="Q23">
         <v>4.2</v>
@@ -6024,7 +6045,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="Q24">
         <v>2.4</v>
@@ -6230,7 +6251,7 @@
         <v>93</v>
       </c>
       <c r="P25" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="Q25">
         <v>4.5</v>
@@ -6311,7 +6332,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ25">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR25">
         <v>1.11</v>
@@ -6642,7 +6663,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="Q27">
         <v>3.4</v>
@@ -6848,7 +6869,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="Q28">
         <v>4.33</v>
@@ -6926,10 +6947,10 @@
         <v>3</v>
       </c>
       <c r="AP28">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AQ28">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AR28">
         <v>1.52</v>
@@ -7341,7 +7362,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ30">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR30">
         <v>2.21</v>
@@ -7466,7 +7487,7 @@
         <v>90</v>
       </c>
       <c r="P31" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="Q31">
         <v>3.75</v>
@@ -7547,7 +7568,7 @@
         <v>2</v>
       </c>
       <c r="AQ31">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AR31">
         <v>1.86</v>
@@ -7753,7 +7774,7 @@
         <v>2.78</v>
       </c>
       <c r="AQ32">
-        <v>0.38</v>
+        <v>0.67</v>
       </c>
       <c r="AR32">
         <v>2.81</v>
@@ -7956,7 +7977,7 @@
         <v>0</v>
       </c>
       <c r="AP33">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ33">
         <v>0</v>
@@ -8084,7 +8105,7 @@
         <v>114</v>
       </c>
       <c r="P34" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="Q34">
         <v>2.3</v>
@@ -8290,7 +8311,7 @@
         <v>91</v>
       </c>
       <c r="P35" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -8780,7 +8801,7 @@
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AQ37">
         <v>1.33</v>
@@ -9114,7 +9135,7 @@
         <v>117</v>
       </c>
       <c r="P39" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="Q39">
         <v>2.2</v>
@@ -9192,7 +9213,7 @@
         <v>0.5</v>
       </c>
       <c r="AP39">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AQ39">
         <v>0.89</v>
@@ -9320,7 +9341,7 @@
         <v>118</v>
       </c>
       <c r="P40" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9398,7 +9419,7 @@
         <v>2</v>
       </c>
       <c r="AP40">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ40">
         <v>1.78</v>
@@ -9526,7 +9547,7 @@
         <v>119</v>
       </c>
       <c r="P41" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="Q41">
         <v>6</v>
@@ -9607,7 +9628,7 @@
         <v>1</v>
       </c>
       <c r="AQ41">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AR41">
         <v>0.92</v>
@@ -10019,7 +10040,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ43">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AR43">
         <v>1.86</v>
@@ -10144,7 +10165,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="Q44">
         <v>3.75</v>
@@ -10350,7 +10371,7 @@
         <v>122</v>
       </c>
       <c r="P45" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="Q45">
         <v>2.88</v>
@@ -10428,7 +10449,7 @@
         <v>0</v>
       </c>
       <c r="AP45">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ45">
         <v>0.5</v>
@@ -10556,7 +10577,7 @@
         <v>123</v>
       </c>
       <c r="P46" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="Q46">
         <v>3.25</v>
@@ -10634,7 +10655,7 @@
         <v>3</v>
       </c>
       <c r="AP46">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AQ46">
         <v>2.67</v>
@@ -10843,7 +10864,7 @@
         <v>2</v>
       </c>
       <c r="AQ47">
-        <v>0.38</v>
+        <v>0.67</v>
       </c>
       <c r="AR47">
         <v>1.61</v>
@@ -10968,7 +10989,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="Q48">
         <v>1.83</v>
@@ -11252,10 +11273,10 @@
         <v>1</v>
       </c>
       <c r="AP49">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AQ49">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR49">
         <v>1.83</v>
@@ -11380,7 +11401,7 @@
         <v>90</v>
       </c>
       <c r="P50" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="Q50">
         <v>5</v>
@@ -11586,7 +11607,7 @@
         <v>126</v>
       </c>
       <c r="P51" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="Q51">
         <v>1.8</v>
@@ -11792,7 +11813,7 @@
         <v>127</v>
       </c>
       <c r="P52" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="Q52">
         <v>3.1</v>
@@ -11998,7 +12019,7 @@
         <v>128</v>
       </c>
       <c r="P53" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="Q53">
         <v>2.3</v>
@@ -12204,7 +12225,7 @@
         <v>106</v>
       </c>
       <c r="P54" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="Q54">
         <v>4</v>
@@ -12822,7 +12843,7 @@
         <v>131</v>
       </c>
       <c r="P57" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="Q57">
         <v>3.25</v>
@@ -13106,10 +13127,10 @@
         <v>0.5</v>
       </c>
       <c r="AP58">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AQ58">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AR58">
         <v>1.61</v>
@@ -13234,7 +13255,7 @@
         <v>133</v>
       </c>
       <c r="P59" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="Q59">
         <v>3.2</v>
@@ -13312,10 +13333,10 @@
         <v>3</v>
       </c>
       <c r="AP59">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ59">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AR59">
         <v>1.74</v>
@@ -13518,7 +13539,7 @@
         <v>1.67</v>
       </c>
       <c r="AP60">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AQ60">
         <v>0.78</v>
@@ -13852,7 +13873,7 @@
         <v>136</v>
       </c>
       <c r="P62" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="Q62">
         <v>3.4</v>
@@ -14058,7 +14079,7 @@
         <v>137</v>
       </c>
       <c r="P63" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="Q63">
         <v>2.38</v>
@@ -14264,7 +14285,7 @@
         <v>138</v>
       </c>
       <c r="P64" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="Q64">
         <v>4.75</v>
@@ -14345,7 +14366,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ64">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AR64">
         <v>1.7</v>
@@ -14676,7 +14697,7 @@
         <v>139</v>
       </c>
       <c r="P66" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q66">
         <v>3.4</v>
@@ -14882,7 +14903,7 @@
         <v>90</v>
       </c>
       <c r="P67" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="Q67">
         <v>5.5</v>
@@ -15088,7 +15109,7 @@
         <v>140</v>
       </c>
       <c r="P68" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="Q68">
         <v>1.73</v>
@@ -15294,7 +15315,7 @@
         <v>90</v>
       </c>
       <c r="P69" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="Q69">
         <v>4</v>
@@ -15500,7 +15521,7 @@
         <v>141</v>
       </c>
       <c r="P70" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="Q70">
         <v>2.1</v>
@@ -15706,7 +15727,7 @@
         <v>93</v>
       </c>
       <c r="P71" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="Q71">
         <v>3.6</v>
@@ -15787,7 +15808,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ71">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR71">
         <v>1.52</v>
@@ -15912,7 +15933,7 @@
         <v>142</v>
       </c>
       <c r="P72" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="Q72">
         <v>3.1</v>
@@ -16118,7 +16139,7 @@
         <v>90</v>
       </c>
       <c r="P73" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="Q73">
         <v>4.33</v>
@@ -16196,7 +16217,7 @@
         <v>2.25</v>
       </c>
       <c r="AP73">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ73">
         <v>2.67</v>
@@ -16402,7 +16423,7 @@
         <v>0.75</v>
       </c>
       <c r="AP74">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ74">
         <v>0.75</v>
@@ -16530,7 +16551,7 @@
         <v>143</v>
       </c>
       <c r="P75" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="Q75">
         <v>3</v>
@@ -16736,7 +16757,7 @@
         <v>144</v>
       </c>
       <c r="P76" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -16817,7 +16838,7 @@
         <v>1</v>
       </c>
       <c r="AQ76">
-        <v>0.38</v>
+        <v>0.67</v>
       </c>
       <c r="AR76">
         <v>1.01</v>
@@ -16942,7 +16963,7 @@
         <v>90</v>
       </c>
       <c r="P77" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17020,7 +17041,7 @@
         <v>1.75</v>
       </c>
       <c r="AP77">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AQ77">
         <v>1.56</v>
@@ -17148,7 +17169,7 @@
         <v>145</v>
       </c>
       <c r="P78" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="Q78">
         <v>2.1</v>
@@ -17226,7 +17247,7 @@
         <v>0</v>
       </c>
       <c r="AP78">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AQ78">
         <v>0.5</v>
@@ -17354,7 +17375,7 @@
         <v>90</v>
       </c>
       <c r="P79" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="Q79">
         <v>3.5</v>
@@ -17432,10 +17453,10 @@
         <v>0.33</v>
       </c>
       <c r="AP79">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ79">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AR79">
         <v>1.36</v>
@@ -17560,7 +17581,7 @@
         <v>146</v>
       </c>
       <c r="P80" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="Q80">
         <v>2.63</v>
@@ -17847,7 +17868,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ81">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AR81">
         <v>1.44</v>
@@ -17972,7 +17993,7 @@
         <v>90</v>
       </c>
       <c r="P82" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="Q82">
         <v>3.6</v>
@@ -18053,7 +18074,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ82">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AR82">
         <v>1.67</v>
@@ -18462,7 +18483,7 @@
         <v>1.75</v>
       </c>
       <c r="AP84">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AQ84">
         <v>1.33</v>
@@ -18796,7 +18817,7 @@
         <v>90</v>
       </c>
       <c r="P86" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="Q86">
         <v>3.2</v>
@@ -18877,7 +18898,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ86">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR86">
         <v>1.37</v>
@@ -19826,7 +19847,7 @@
         <v>153</v>
       </c>
       <c r="P91" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="Q91">
         <v>4.33</v>
@@ -20032,7 +20053,7 @@
         <v>154</v>
       </c>
       <c r="P92" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="Q92">
         <v>1.91</v>
@@ -20238,7 +20259,7 @@
         <v>144</v>
       </c>
       <c r="P93" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -20319,7 +20340,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ93">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AR93">
         <v>1.3</v>
@@ -20444,7 +20465,7 @@
         <v>155</v>
       </c>
       <c r="P94" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -20522,7 +20543,7 @@
         <v>1</v>
       </c>
       <c r="AP94">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AQ94">
         <v>0.78</v>
@@ -20650,7 +20671,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="Q95">
         <v>8.5</v>
@@ -20731,7 +20752,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ95">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AR95">
         <v>1.33</v>
@@ -20856,7 +20877,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="Q96">
         <v>3.2</v>
@@ -21062,7 +21083,7 @@
         <v>90</v>
       </c>
       <c r="P97" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="Q97">
         <v>2.88</v>
@@ -21140,10 +21161,10 @@
         <v>1</v>
       </c>
       <c r="AP97">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ97">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AR97">
         <v>1.67</v>
@@ -21268,7 +21289,7 @@
         <v>158</v>
       </c>
       <c r="P98" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="Q98">
         <v>3.5</v>
@@ -21346,10 +21367,10 @@
         <v>0.75</v>
       </c>
       <c r="AP98">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ98">
-        <v>0.38</v>
+        <v>0.67</v>
       </c>
       <c r="AR98">
         <v>1.3</v>
@@ -21474,7 +21495,7 @@
         <v>90</v>
       </c>
       <c r="P99" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="Q99">
         <v>3.75</v>
@@ -21758,7 +21779,7 @@
         <v>0.2</v>
       </c>
       <c r="AP100">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AQ100">
         <v>0.11</v>
@@ -21886,7 +21907,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="Q101">
         <v>2.05</v>
@@ -21967,7 +21988,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ101">
-        <v>0.38</v>
+        <v>0.67</v>
       </c>
       <c r="AR101">
         <v>1.51</v>
@@ -22173,7 +22194,7 @@
         <v>2.78</v>
       </c>
       <c r="AQ102">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AR102">
         <v>2.25</v>
@@ -22298,7 +22319,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22376,7 +22397,7 @@
         <v>2.5</v>
       </c>
       <c r="AP103">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AQ103">
         <v>2.67</v>
@@ -22994,7 +23015,7 @@
         <v>0.2</v>
       </c>
       <c r="AP106">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AQ106">
         <v>0.13</v>
@@ -23328,7 +23349,7 @@
         <v>90</v>
       </c>
       <c r="P108" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="Q108">
         <v>2.6</v>
@@ -23534,7 +23555,7 @@
         <v>166</v>
       </c>
       <c r="P109" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="Q109">
         <v>2.38</v>
@@ -23740,7 +23761,7 @@
         <v>90</v>
       </c>
       <c r="P110" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="Q110">
         <v>3.4</v>
@@ -24024,7 +24045,7 @@
         <v>0.17</v>
       </c>
       <c r="AP111">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ111">
         <v>0.11</v>
@@ -24152,7 +24173,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="Q112">
         <v>2.88</v>
@@ -24564,7 +24585,7 @@
         <v>170</v>
       </c>
       <c r="P114" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="Q114">
         <v>4.33</v>
@@ -24642,7 +24663,7 @@
         <v>1.83</v>
       </c>
       <c r="AP114">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ114">
         <v>1.56</v>
@@ -24770,7 +24791,7 @@
         <v>90</v>
       </c>
       <c r="P115" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="Q115">
         <v>3</v>
@@ -25182,7 +25203,7 @@
         <v>172</v>
       </c>
       <c r="P117" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q117">
         <v>2.6</v>
@@ -25260,10 +25281,10 @@
         <v>1.33</v>
       </c>
       <c r="AP117">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AQ117">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR117">
         <v>1.77</v>
@@ -25388,7 +25409,7 @@
         <v>173</v>
       </c>
       <c r="P118" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="Q118">
         <v>3.1</v>
@@ -25469,7 +25490,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ118">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AR118">
         <v>1.45</v>
@@ -25672,10 +25693,10 @@
         <v>0.5</v>
       </c>
       <c r="AP119">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AQ119">
-        <v>0.38</v>
+        <v>0.67</v>
       </c>
       <c r="AR119">
         <v>1.36</v>
@@ -25881,7 +25902,7 @@
         <v>2</v>
       </c>
       <c r="AQ120">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AR120">
         <v>1.48</v>
@@ -26087,7 +26108,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ121">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AR121">
         <v>1.48</v>
@@ -26212,7 +26233,7 @@
         <v>176</v>
       </c>
       <c r="P122" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="Q122">
         <v>2.05</v>
@@ -26418,7 +26439,7 @@
         <v>90</v>
       </c>
       <c r="P123" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="Q123">
         <v>4.75</v>
@@ -26702,7 +26723,7 @@
         <v>0</v>
       </c>
       <c r="AP124">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AQ124">
         <v>0</v>
@@ -27242,7 +27263,7 @@
         <v>90</v>
       </c>
       <c r="P127" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="Q127">
         <v>5</v>
@@ -27654,7 +27675,7 @@
         <v>148</v>
       </c>
       <c r="P129" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="Q129">
         <v>2.88</v>
@@ -27860,7 +27881,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="Q130">
         <v>4.33</v>
@@ -28147,7 +28168,7 @@
         <v>1</v>
       </c>
       <c r="AQ131">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AR131">
         <v>1.24</v>
@@ -28272,7 +28293,7 @@
         <v>181</v>
       </c>
       <c r="P132" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="Q132">
         <v>3.5</v>
@@ -28350,10 +28371,10 @@
         <v>1.14</v>
       </c>
       <c r="AP132">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ132">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR132">
         <v>1.36</v>
@@ -28478,7 +28499,7 @@
         <v>90</v>
       </c>
       <c r="P133" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="Q133">
         <v>3.5</v>
@@ -28968,7 +28989,7 @@
         <v>1.29</v>
       </c>
       <c r="AP135">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ135">
         <v>1.33</v>
@@ -29302,7 +29323,7 @@
         <v>185</v>
       </c>
       <c r="P137" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="Q137">
         <v>3.4</v>
@@ -29383,7 +29404,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ137">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AR137">
         <v>1.51</v>
@@ -29508,7 +29529,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="Q138">
         <v>2.88</v>
@@ -29714,7 +29735,7 @@
         <v>187</v>
       </c>
       <c r="P139" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="Q139">
         <v>4</v>
@@ -29920,7 +29941,7 @@
         <v>129</v>
       </c>
       <c r="P140" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="Q140">
         <v>2.2</v>
@@ -29998,7 +30019,7 @@
         <v>0.75</v>
       </c>
       <c r="AP140">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AQ140">
         <v>0.78</v>
@@ -30204,7 +30225,7 @@
         <v>0</v>
       </c>
       <c r="AP141">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AQ141">
         <v>0</v>
@@ -30410,10 +30431,10 @@
         <v>1</v>
       </c>
       <c r="AP142">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AQ142">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AR142">
         <v>1.73</v>
@@ -30825,7 +30846,7 @@
         <v>0.88</v>
       </c>
       <c r="AQ144">
-        <v>0.38</v>
+        <v>0.67</v>
       </c>
       <c r="AR144">
         <v>1.26</v>
@@ -30950,7 +30971,7 @@
         <v>191</v>
       </c>
       <c r="P145" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="Q145">
         <v>1.8</v>
@@ -31156,7 +31177,7 @@
         <v>192</v>
       </c>
       <c r="P146" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="Q146">
         <v>4.33</v>
@@ -31237,7 +31258,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ146">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AR146">
         <v>1.45</v>
@@ -31568,7 +31589,7 @@
         <v>193</v>
       </c>
       <c r="P148" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="Q148">
         <v>3.6</v>
@@ -31774,7 +31795,7 @@
         <v>194</v>
       </c>
       <c r="P149" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="Q149">
         <v>3.2</v>
@@ -31855,7 +31876,7 @@
         <v>1</v>
       </c>
       <c r="AQ149">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AR149">
         <v>1.18</v>
@@ -31980,7 +32001,7 @@
         <v>195</v>
       </c>
       <c r="P150" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="Q150">
         <v>3.5</v>
@@ -32058,7 +32079,7 @@
         <v>2.63</v>
       </c>
       <c r="AP150">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ150">
         <v>2.67</v>
@@ -32186,7 +32207,7 @@
         <v>196</v>
       </c>
       <c r="P151" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="Q151">
         <v>5.25</v>
@@ -32392,7 +32413,7 @@
         <v>197</v>
       </c>
       <c r="P152" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="Q152">
         <v>2.6</v>
@@ -32470,7 +32491,7 @@
         <v>1.13</v>
       </c>
       <c r="AP152">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ152">
         <v>1.33</v>
@@ -32598,7 +32619,7 @@
         <v>198</v>
       </c>
       <c r="P153" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="Q153">
         <v>2.3</v>
@@ -32961,6 +32982,1036 @@
       </c>
       <c r="BP154">
         <v>1.41</v>
+      </c>
+    </row>
+    <row r="155" spans="1:68">
+      <c r="A155" s="1">
+        <v>154</v>
+      </c>
+      <c r="B155">
+        <v>7468514</v>
+      </c>
+      <c r="C155" t="s">
+        <v>68</v>
+      </c>
+      <c r="D155" t="s">
+        <v>69</v>
+      </c>
+      <c r="E155" s="2">
+        <v>45674.625</v>
+      </c>
+      <c r="F155">
+        <v>18</v>
+      </c>
+      <c r="G155" t="s">
+        <v>75</v>
+      </c>
+      <c r="H155" t="s">
+        <v>73</v>
+      </c>
+      <c r="I155">
+        <v>0</v>
+      </c>
+      <c r="J155">
+        <v>1</v>
+      </c>
+      <c r="K155">
+        <v>1</v>
+      </c>
+      <c r="L155">
+        <v>2</v>
+      </c>
+      <c r="M155">
+        <v>1</v>
+      </c>
+      <c r="N155">
+        <v>3</v>
+      </c>
+      <c r="O155" t="s">
+        <v>200</v>
+      </c>
+      <c r="P155" t="s">
+        <v>291</v>
+      </c>
+      <c r="Q155">
+        <v>5</v>
+      </c>
+      <c r="R155">
+        <v>2.5</v>
+      </c>
+      <c r="S155">
+        <v>2.1</v>
+      </c>
+      <c r="T155">
+        <v>1.29</v>
+      </c>
+      <c r="U155">
+        <v>3.5</v>
+      </c>
+      <c r="V155">
+        <v>2.25</v>
+      </c>
+      <c r="W155">
+        <v>1.57</v>
+      </c>
+      <c r="X155">
+        <v>5.5</v>
+      </c>
+      <c r="Y155">
+        <v>1.14</v>
+      </c>
+      <c r="Z155">
+        <v>4.3</v>
+      </c>
+      <c r="AA155">
+        <v>4.1</v>
+      </c>
+      <c r="AB155">
+        <v>1.71</v>
+      </c>
+      <c r="AC155">
+        <v>1.02</v>
+      </c>
+      <c r="AD155">
+        <v>21</v>
+      </c>
+      <c r="AE155">
+        <v>1.16</v>
+      </c>
+      <c r="AF155">
+        <v>5.5</v>
+      </c>
+      <c r="AG155">
+        <v>1.48</v>
+      </c>
+      <c r="AH155">
+        <v>2.54</v>
+      </c>
+      <c r="AI155">
+        <v>1.62</v>
+      </c>
+      <c r="AJ155">
+        <v>2.2</v>
+      </c>
+      <c r="AK155">
+        <v>2.25</v>
+      </c>
+      <c r="AL155">
+        <v>1.22</v>
+      </c>
+      <c r="AM155">
+        <v>1.17</v>
+      </c>
+      <c r="AN155">
+        <v>1</v>
+      </c>
+      <c r="AO155">
+        <v>1.75</v>
+      </c>
+      <c r="AP155">
+        <v>1.2</v>
+      </c>
+      <c r="AQ155">
+        <v>1.56</v>
+      </c>
+      <c r="AR155">
+        <v>1.44</v>
+      </c>
+      <c r="AS155">
+        <v>1.5</v>
+      </c>
+      <c r="AT155">
+        <v>2.94</v>
+      </c>
+      <c r="AU155">
+        <v>6</v>
+      </c>
+      <c r="AV155">
+        <v>11</v>
+      </c>
+      <c r="AW155">
+        <v>7</v>
+      </c>
+      <c r="AX155">
+        <v>18</v>
+      </c>
+      <c r="AY155">
+        <v>15</v>
+      </c>
+      <c r="AZ155">
+        <v>35</v>
+      </c>
+      <c r="BA155">
+        <v>4</v>
+      </c>
+      <c r="BB155">
+        <v>16</v>
+      </c>
+      <c r="BC155">
+        <v>20</v>
+      </c>
+      <c r="BD155">
+        <v>2.65</v>
+      </c>
+      <c r="BE155">
+        <v>6.4</v>
+      </c>
+      <c r="BF155">
+        <v>1.57</v>
+      </c>
+      <c r="BG155">
+        <v>1.3</v>
+      </c>
+      <c r="BH155">
+        <v>3.05</v>
+      </c>
+      <c r="BI155">
+        <v>1.55</v>
+      </c>
+      <c r="BJ155">
+        <v>2.28</v>
+      </c>
+      <c r="BK155">
+        <v>1.89</v>
+      </c>
+      <c r="BL155">
+        <v>1.8</v>
+      </c>
+      <c r="BM155">
+        <v>2.38</v>
+      </c>
+      <c r="BN155">
+        <v>1.5</v>
+      </c>
+      <c r="BO155">
+        <v>3.05</v>
+      </c>
+      <c r="BP155">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="156" spans="1:68">
+      <c r="A156" s="1">
+        <v>155</v>
+      </c>
+      <c r="B156">
+        <v>7468511</v>
+      </c>
+      <c r="C156" t="s">
+        <v>68</v>
+      </c>
+      <c r="D156" t="s">
+        <v>69</v>
+      </c>
+      <c r="E156" s="2">
+        <v>45674.71180555555</v>
+      </c>
+      <c r="F156">
+        <v>18</v>
+      </c>
+      <c r="G156" t="s">
+        <v>81</v>
+      </c>
+      <c r="H156" t="s">
+        <v>86</v>
+      </c>
+      <c r="I156">
+        <v>0</v>
+      </c>
+      <c r="J156">
+        <v>1</v>
+      </c>
+      <c r="K156">
+        <v>1</v>
+      </c>
+      <c r="L156">
+        <v>2</v>
+      </c>
+      <c r="M156">
+        <v>1</v>
+      </c>
+      <c r="N156">
+        <v>3</v>
+      </c>
+      <c r="O156" t="s">
+        <v>201</v>
+      </c>
+      <c r="P156" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q156">
+        <v>2.5</v>
+      </c>
+      <c r="R156">
+        <v>2.25</v>
+      </c>
+      <c r="S156">
+        <v>4.33</v>
+      </c>
+      <c r="T156">
+        <v>1.36</v>
+      </c>
+      <c r="U156">
+        <v>3</v>
+      </c>
+      <c r="V156">
+        <v>2.63</v>
+      </c>
+      <c r="W156">
+        <v>1.44</v>
+      </c>
+      <c r="X156">
+        <v>7</v>
+      </c>
+      <c r="Y156">
+        <v>1.1</v>
+      </c>
+      <c r="Z156">
+        <v>1.72</v>
+      </c>
+      <c r="AA156">
+        <v>3.9</v>
+      </c>
+      <c r="AB156">
+        <v>4.5</v>
+      </c>
+      <c r="AC156">
+        <v>1.04</v>
+      </c>
+      <c r="AD156">
+        <v>13</v>
+      </c>
+      <c r="AE156">
+        <v>1.26</v>
+      </c>
+      <c r="AF156">
+        <v>4</v>
+      </c>
+      <c r="AG156">
+        <v>1.79</v>
+      </c>
+      <c r="AH156">
+        <v>2.07</v>
+      </c>
+      <c r="AI156">
+        <v>1.7</v>
+      </c>
+      <c r="AJ156">
+        <v>2.05</v>
+      </c>
+      <c r="AK156">
+        <v>1.24</v>
+      </c>
+      <c r="AL156">
+        <v>1.27</v>
+      </c>
+      <c r="AM156">
+        <v>1.9</v>
+      </c>
+      <c r="AN156">
+        <v>1.88</v>
+      </c>
+      <c r="AO156">
+        <v>1.33</v>
+      </c>
+      <c r="AP156">
+        <v>2</v>
+      </c>
+      <c r="AQ156">
+        <v>1.2</v>
+      </c>
+      <c r="AR156">
+        <v>1.36</v>
+      </c>
+      <c r="AS156">
+        <v>1.48</v>
+      </c>
+      <c r="AT156">
+        <v>2.84</v>
+      </c>
+      <c r="AU156">
+        <v>5</v>
+      </c>
+      <c r="AV156">
+        <v>4</v>
+      </c>
+      <c r="AW156">
+        <v>7</v>
+      </c>
+      <c r="AX156">
+        <v>8</v>
+      </c>
+      <c r="AY156">
+        <v>13</v>
+      </c>
+      <c r="AZ156">
+        <v>14</v>
+      </c>
+      <c r="BA156">
+        <v>7</v>
+      </c>
+      <c r="BB156">
+        <v>7</v>
+      </c>
+      <c r="BC156">
+        <v>14</v>
+      </c>
+      <c r="BD156">
+        <v>1.56</v>
+      </c>
+      <c r="BE156">
+        <v>6.4</v>
+      </c>
+      <c r="BF156">
+        <v>2.7</v>
+      </c>
+      <c r="BG156">
+        <v>1.43</v>
+      </c>
+      <c r="BH156">
+        <v>2.55</v>
+      </c>
+      <c r="BI156">
+        <v>1.72</v>
+      </c>
+      <c r="BJ156">
+        <v>1.98</v>
+      </c>
+      <c r="BK156">
+        <v>2.15</v>
+      </c>
+      <c r="BL156">
+        <v>1.61</v>
+      </c>
+      <c r="BM156">
+        <v>2.8</v>
+      </c>
+      <c r="BN156">
+        <v>1.37</v>
+      </c>
+      <c r="BO156">
+        <v>3.7</v>
+      </c>
+      <c r="BP156">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="157" spans="1:68">
+      <c r="A157" s="1">
+        <v>156</v>
+      </c>
+      <c r="B157">
+        <v>7468510</v>
+      </c>
+      <c r="C157" t="s">
+        <v>68</v>
+      </c>
+      <c r="D157" t="s">
+        <v>69</v>
+      </c>
+      <c r="E157" s="2">
+        <v>45675.54166666666</v>
+      </c>
+      <c r="F157">
+        <v>18</v>
+      </c>
+      <c r="G157" t="s">
+        <v>83</v>
+      </c>
+      <c r="H157" t="s">
+        <v>79</v>
+      </c>
+      <c r="I157">
+        <v>1</v>
+      </c>
+      <c r="J157">
+        <v>0</v>
+      </c>
+      <c r="K157">
+        <v>1</v>
+      </c>
+      <c r="L157">
+        <v>1</v>
+      </c>
+      <c r="M157">
+        <v>2</v>
+      </c>
+      <c r="N157">
+        <v>3</v>
+      </c>
+      <c r="O157" t="s">
+        <v>202</v>
+      </c>
+      <c r="P157" t="s">
+        <v>292</v>
+      </c>
+      <c r="Q157">
+        <v>4.33</v>
+      </c>
+      <c r="R157">
+        <v>2.4</v>
+      </c>
+      <c r="S157">
+        <v>2.3</v>
+      </c>
+      <c r="T157">
+        <v>1.29</v>
+      </c>
+      <c r="U157">
+        <v>3.5</v>
+      </c>
+      <c r="V157">
+        <v>2.38</v>
+      </c>
+      <c r="W157">
+        <v>1.53</v>
+      </c>
+      <c r="X157">
+        <v>5.5</v>
+      </c>
+      <c r="Y157">
+        <v>1.14</v>
+      </c>
+      <c r="Z157">
+        <v>4.5</v>
+      </c>
+      <c r="AA157">
+        <v>3.95</v>
+      </c>
+      <c r="AB157">
+        <v>1.73</v>
+      </c>
+      <c r="AC157">
+        <v>1.02</v>
+      </c>
+      <c r="AD157">
+        <v>19</v>
+      </c>
+      <c r="AE157">
+        <v>1.18</v>
+      </c>
+      <c r="AF157">
+        <v>5</v>
+      </c>
+      <c r="AG157">
+        <v>1.61</v>
+      </c>
+      <c r="AH157">
+        <v>2.32</v>
+      </c>
+      <c r="AI157">
+        <v>1.57</v>
+      </c>
+      <c r="AJ157">
+        <v>2.25</v>
+      </c>
+      <c r="AK157">
+        <v>2</v>
+      </c>
+      <c r="AL157">
+        <v>1.24</v>
+      </c>
+      <c r="AM157">
+        <v>1.22</v>
+      </c>
+      <c r="AN157">
+        <v>1.38</v>
+      </c>
+      <c r="AO157">
+        <v>2.25</v>
+      </c>
+      <c r="AP157">
+        <v>1.22</v>
+      </c>
+      <c r="AQ157">
+        <v>2.33</v>
+      </c>
+      <c r="AR157">
+        <v>1.67</v>
+      </c>
+      <c r="AS157">
+        <v>2.23</v>
+      </c>
+      <c r="AT157">
+        <v>3.9</v>
+      </c>
+      <c r="AU157">
+        <v>6</v>
+      </c>
+      <c r="AV157">
+        <v>8</v>
+      </c>
+      <c r="AW157">
+        <v>5</v>
+      </c>
+      <c r="AX157">
+        <v>2</v>
+      </c>
+      <c r="AY157">
+        <v>14</v>
+      </c>
+      <c r="AZ157">
+        <v>12</v>
+      </c>
+      <c r="BA157">
+        <v>6</v>
+      </c>
+      <c r="BB157">
+        <v>1</v>
+      </c>
+      <c r="BC157">
+        <v>7</v>
+      </c>
+      <c r="BD157">
+        <v>2.65</v>
+      </c>
+      <c r="BE157">
+        <v>6.5</v>
+      </c>
+      <c r="BF157">
+        <v>1.58</v>
+      </c>
+      <c r="BG157">
+        <v>1.33</v>
+      </c>
+      <c r="BH157">
+        <v>2.95</v>
+      </c>
+      <c r="BI157">
+        <v>1.57</v>
+      </c>
+      <c r="BJ157">
+        <v>2.23</v>
+      </c>
+      <c r="BK157">
+        <v>1.94</v>
+      </c>
+      <c r="BL157">
+        <v>1.76</v>
+      </c>
+      <c r="BM157">
+        <v>2.43</v>
+      </c>
+      <c r="BN157">
+        <v>1.48</v>
+      </c>
+      <c r="BO157">
+        <v>3.2</v>
+      </c>
+      <c r="BP157">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="158" spans="1:68">
+      <c r="A158" s="1">
+        <v>157</v>
+      </c>
+      <c r="B158">
+        <v>7468517</v>
+      </c>
+      <c r="C158" t="s">
+        <v>68</v>
+      </c>
+      <c r="D158" t="s">
+        <v>69</v>
+      </c>
+      <c r="E158" s="2">
+        <v>45675.625</v>
+      </c>
+      <c r="F158">
+        <v>18</v>
+      </c>
+      <c r="G158" t="s">
+        <v>78</v>
+      </c>
+      <c r="H158" t="s">
+        <v>71</v>
+      </c>
+      <c r="I158">
+        <v>0</v>
+      </c>
+      <c r="J158">
+        <v>1</v>
+      </c>
+      <c r="K158">
+        <v>1</v>
+      </c>
+      <c r="L158">
+        <v>1</v>
+      </c>
+      <c r="M158">
+        <v>2</v>
+      </c>
+      <c r="N158">
+        <v>3</v>
+      </c>
+      <c r="O158" t="s">
+        <v>203</v>
+      </c>
+      <c r="P158" t="s">
+        <v>293</v>
+      </c>
+      <c r="Q158">
+        <v>2.6</v>
+      </c>
+      <c r="R158">
+        <v>2.1</v>
+      </c>
+      <c r="S158">
+        <v>4.5</v>
+      </c>
+      <c r="T158">
+        <v>1.44</v>
+      </c>
+      <c r="U158">
+        <v>2.63</v>
+      </c>
+      <c r="V158">
+        <v>3.25</v>
+      </c>
+      <c r="W158">
+        <v>1.33</v>
+      </c>
+      <c r="X158">
+        <v>9</v>
+      </c>
+      <c r="Y158">
+        <v>1.07</v>
+      </c>
+      <c r="Z158">
+        <v>2</v>
+      </c>
+      <c r="AA158">
+        <v>3.4</v>
+      </c>
+      <c r="AB158">
+        <v>3.85</v>
+      </c>
+      <c r="AC158">
+        <v>1.06</v>
+      </c>
+      <c r="AD158">
+        <v>10</v>
+      </c>
+      <c r="AE158">
+        <v>1.36</v>
+      </c>
+      <c r="AF158">
+        <v>3.2</v>
+      </c>
+      <c r="AG158">
+        <v>2.04</v>
+      </c>
+      <c r="AH158">
+        <v>1.78</v>
+      </c>
+      <c r="AI158">
+        <v>1.91</v>
+      </c>
+      <c r="AJ158">
+        <v>1.91</v>
+      </c>
+      <c r="AK158">
+        <v>1.26</v>
+      </c>
+      <c r="AL158">
+        <v>1.26</v>
+      </c>
+      <c r="AM158">
+        <v>1.87</v>
+      </c>
+      <c r="AN158">
+        <v>1.78</v>
+      </c>
+      <c r="AO158">
+        <v>0.38</v>
+      </c>
+      <c r="AP158">
+        <v>1.6</v>
+      </c>
+      <c r="AQ158">
+        <v>0.67</v>
+      </c>
+      <c r="AR158">
+        <v>1.48</v>
+      </c>
+      <c r="AS158">
+        <v>1.32</v>
+      </c>
+      <c r="AT158">
+        <v>2.8</v>
+      </c>
+      <c r="AU158">
+        <v>11</v>
+      </c>
+      <c r="AV158">
+        <v>4</v>
+      </c>
+      <c r="AW158">
+        <v>12</v>
+      </c>
+      <c r="AX158">
+        <v>6</v>
+      </c>
+      <c r="AY158">
+        <v>25</v>
+      </c>
+      <c r="AZ158">
+        <v>10</v>
+      </c>
+      <c r="BA158">
+        <v>4</v>
+      </c>
+      <c r="BB158">
+        <v>4</v>
+      </c>
+      <c r="BC158">
+        <v>8</v>
+      </c>
+      <c r="BD158">
+        <v>1.45</v>
+      </c>
+      <c r="BE158">
+        <v>6.75</v>
+      </c>
+      <c r="BF158">
+        <v>3.15</v>
+      </c>
+      <c r="BG158">
+        <v>1.46</v>
+      </c>
+      <c r="BH158">
+        <v>2.5</v>
+      </c>
+      <c r="BI158">
+        <v>1.75</v>
+      </c>
+      <c r="BJ158">
+        <v>1.95</v>
+      </c>
+      <c r="BK158">
+        <v>2.2</v>
+      </c>
+      <c r="BL158">
+        <v>1.58</v>
+      </c>
+      <c r="BM158">
+        <v>2.9</v>
+      </c>
+      <c r="BN158">
+        <v>1.35</v>
+      </c>
+      <c r="BO158">
+        <v>3.7</v>
+      </c>
+      <c r="BP158">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="159" spans="1:68">
+      <c r="A159" s="1">
+        <v>158</v>
+      </c>
+      <c r="B159">
+        <v>7468512</v>
+      </c>
+      <c r="C159" t="s">
+        <v>68</v>
+      </c>
+      <c r="D159" t="s">
+        <v>69</v>
+      </c>
+      <c r="E159" s="2">
+        <v>45675.71180555555</v>
+      </c>
+      <c r="F159">
+        <v>18</v>
+      </c>
+      <c r="G159" t="s">
+        <v>80</v>
+      </c>
+      <c r="H159" t="s">
+        <v>76</v>
+      </c>
+      <c r="I159">
+        <v>0</v>
+      </c>
+      <c r="J159">
+        <v>0</v>
+      </c>
+      <c r="K159">
+        <v>0</v>
+      </c>
+      <c r="L159">
+        <v>0</v>
+      </c>
+      <c r="M159">
+        <v>0</v>
+      </c>
+      <c r="N159">
+        <v>0</v>
+      </c>
+      <c r="O159" t="s">
+        <v>90</v>
+      </c>
+      <c r="P159" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q159">
+        <v>2.4</v>
+      </c>
+      <c r="R159">
+        <v>2.3</v>
+      </c>
+      <c r="S159">
+        <v>4.33</v>
+      </c>
+      <c r="T159">
+        <v>1.33</v>
+      </c>
+      <c r="U159">
+        <v>3.25</v>
+      </c>
+      <c r="V159">
+        <v>2.5</v>
+      </c>
+      <c r="W159">
+        <v>1.5</v>
+      </c>
+      <c r="X159">
+        <v>6.5</v>
+      </c>
+      <c r="Y159">
+        <v>1.11</v>
+      </c>
+      <c r="Z159">
+        <v>1.9</v>
+      </c>
+      <c r="AA159">
+        <v>3.8</v>
+      </c>
+      <c r="AB159">
+        <v>3.9</v>
+      </c>
+      <c r="AC159">
+        <v>1.03</v>
+      </c>
+      <c r="AD159">
+        <v>15</v>
+      </c>
+      <c r="AE159">
+        <v>1.22</v>
+      </c>
+      <c r="AF159">
+        <v>4.33</v>
+      </c>
+      <c r="AG159">
+        <v>1.65</v>
+      </c>
+      <c r="AH159">
+        <v>2.23</v>
+      </c>
+      <c r="AI159">
+        <v>1.67</v>
+      </c>
+      <c r="AJ159">
+        <v>2.1</v>
+      </c>
+      <c r="AK159">
+        <v>1.23</v>
+      </c>
+      <c r="AL159">
+        <v>1.25</v>
+      </c>
+      <c r="AM159">
+        <v>1.98</v>
+      </c>
+      <c r="AN159">
+        <v>2</v>
+      </c>
+      <c r="AO159">
+        <v>1.25</v>
+      </c>
+      <c r="AP159">
+        <v>1.89</v>
+      </c>
+      <c r="AQ159">
+        <v>1.22</v>
+      </c>
+      <c r="AR159">
+        <v>1.74</v>
+      </c>
+      <c r="AS159">
+        <v>1.17</v>
+      </c>
+      <c r="AT159">
+        <v>2.91</v>
+      </c>
+      <c r="AU159">
+        <v>4</v>
+      </c>
+      <c r="AV159">
+        <v>6</v>
+      </c>
+      <c r="AW159">
+        <v>7</v>
+      </c>
+      <c r="AX159">
+        <v>7</v>
+      </c>
+      <c r="AY159">
+        <v>13</v>
+      </c>
+      <c r="AZ159">
+        <v>15</v>
+      </c>
+      <c r="BA159">
+        <v>8</v>
+      </c>
+      <c r="BB159">
+        <v>5</v>
+      </c>
+      <c r="BC159">
+        <v>13</v>
+      </c>
+      <c r="BD159">
+        <v>1.53</v>
+      </c>
+      <c r="BE159">
+        <v>6.4</v>
+      </c>
+      <c r="BF159">
+        <v>2.8</v>
+      </c>
+      <c r="BG159">
+        <v>1.33</v>
+      </c>
+      <c r="BH159">
+        <v>2.95</v>
+      </c>
+      <c r="BI159">
+        <v>1.56</v>
+      </c>
+      <c r="BJ159">
+        <v>2.23</v>
+      </c>
+      <c r="BK159">
+        <v>1.92</v>
+      </c>
+      <c r="BL159">
+        <v>1.77</v>
+      </c>
+      <c r="BM159">
+        <v>2.43</v>
+      </c>
+      <c r="BN159">
+        <v>1.48</v>
+      </c>
+      <c r="BO159">
+        <v>3.15</v>
+      </c>
+      <c r="BP159">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/France Ligue 1_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/France Ligue 1_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1016" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="297">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -628,6 +628,18 @@
     <t>['77']</t>
   </si>
   <si>
+    <t>['86']</t>
+  </si>
+  <si>
+    <t>['18', '47']</t>
+  </si>
+  <si>
+    <t>['26']</t>
+  </si>
+  <si>
+    <t>['68']</t>
+  </si>
+  <si>
     <t>['3', '84', '86', '90']</t>
   </si>
   <si>
@@ -691,9 +703,6 @@
     <t>['90+6']</t>
   </si>
   <si>
-    <t>['68']</t>
-  </si>
-  <si>
     <t>['18']</t>
   </si>
   <si>
@@ -731,9 +740,6 @@
   </si>
   <si>
     <t>['52']</t>
-  </si>
-  <si>
-    <t>['86']</t>
   </si>
   <si>
     <t>['20', '79']</t>
@@ -896,6 +902,9 @@
   </si>
   <si>
     <t>['27', '73']</t>
+  </si>
+  <si>
+    <t>['23']</t>
   </si>
 </sst>
 </file>
@@ -1257,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP159"/>
+  <dimension ref="A1:BP163"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1513,7 +1522,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="Q2">
         <v>6</v>
@@ -1719,7 +1728,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="Q3">
         <v>3.4</v>
@@ -1925,7 +1934,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -2337,7 +2346,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="Q6">
         <v>3.75</v>
@@ -2543,7 +2552,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -2624,7 +2633,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ7">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2830,7 +2839,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ8">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3033,7 +3042,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AQ9">
         <v>1.78</v>
@@ -3573,7 +3582,7 @@
         <v>90</v>
       </c>
       <c r="P12" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="Q12">
         <v>2.8</v>
@@ -3985,7 +3994,7 @@
         <v>90</v>
       </c>
       <c r="P14" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="Q14">
         <v>2.65</v>
@@ -4063,10 +4072,10 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AQ14">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4397,7 +4406,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="Q16">
         <v>3.6</v>
@@ -4684,7 +4693,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ17">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5015,7 +5024,7 @@
         <v>101</v>
       </c>
       <c r="P19" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="Q19">
         <v>2.1</v>
@@ -5093,7 +5102,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ19">
         <v>1.38</v>
@@ -5221,7 +5230,7 @@
         <v>102</v>
       </c>
       <c r="P20" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="Q20">
         <v>2.45</v>
@@ -5302,7 +5311,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ20">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR20">
         <v>0.4</v>
@@ -5633,7 +5642,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="Q22">
         <v>2.8</v>
@@ -5714,7 +5723,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ22">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR22">
         <v>1.21</v>
@@ -5839,7 +5848,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="Q23">
         <v>4.2</v>
@@ -6045,7 +6054,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="Q24">
         <v>2.4</v>
@@ -6251,7 +6260,7 @@
         <v>93</v>
       </c>
       <c r="P25" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="Q25">
         <v>4.5</v>
@@ -6329,7 +6338,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AQ25">
         <v>1.2</v>
@@ -6538,7 +6547,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ26">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR26">
         <v>0.74</v>
@@ -6663,7 +6672,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="Q27">
         <v>3.4</v>
@@ -6869,7 +6878,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="Q28">
         <v>4.33</v>
@@ -7153,7 +7162,7 @@
         <v>3</v>
       </c>
       <c r="AP29">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AQ29">
         <v>1.56</v>
@@ -7359,7 +7368,7 @@
         <v>1.5</v>
       </c>
       <c r="AP30">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ30">
         <v>1.2</v>
@@ -7487,7 +7496,7 @@
         <v>90</v>
       </c>
       <c r="P31" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="Q31">
         <v>3.75</v>
@@ -8105,7 +8114,7 @@
         <v>114</v>
       </c>
       <c r="P34" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="Q34">
         <v>2.3</v>
@@ -8311,7 +8320,7 @@
         <v>91</v>
       </c>
       <c r="P35" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -8598,7 +8607,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ36">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AR36">
         <v>1.04</v>
@@ -9135,7 +9144,7 @@
         <v>117</v>
       </c>
       <c r="P39" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="Q39">
         <v>2.2</v>
@@ -9216,7 +9225,7 @@
         <v>2</v>
       </c>
       <c r="AQ39">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR39">
         <v>1.47</v>
@@ -9341,7 +9350,7 @@
         <v>118</v>
       </c>
       <c r="P40" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -9547,7 +9556,7 @@
         <v>119</v>
       </c>
       <c r="P41" t="s">
-        <v>225</v>
+        <v>207</v>
       </c>
       <c r="Q41">
         <v>6</v>
@@ -9834,7 +9843,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ42">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AR42">
         <v>1.39</v>
@@ -10165,7 +10174,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="Q44">
         <v>3.75</v>
@@ -10243,10 +10252,10 @@
         <v>2</v>
       </c>
       <c r="AP44">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AQ44">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR44">
         <v>1.49</v>
@@ -10371,7 +10380,7 @@
         <v>122</v>
       </c>
       <c r="P45" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q45">
         <v>2.88</v>
@@ -10452,7 +10461,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ45">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR45">
         <v>1.4</v>
@@ -10577,7 +10586,7 @@
         <v>123</v>
       </c>
       <c r="P46" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q46">
         <v>3.25</v>
@@ -10989,7 +10998,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q48">
         <v>1.83</v>
@@ -11401,7 +11410,7 @@
         <v>90</v>
       </c>
       <c r="P50" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q50">
         <v>5</v>
@@ -11607,7 +11616,7 @@
         <v>126</v>
       </c>
       <c r="P51" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q51">
         <v>1.8</v>
@@ -11813,7 +11822,7 @@
         <v>127</v>
       </c>
       <c r="P52" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q52">
         <v>3.1</v>
@@ -12019,7 +12028,7 @@
         <v>128</v>
       </c>
       <c r="P53" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="Q53">
         <v>2.3</v>
@@ -12225,7 +12234,7 @@
         <v>106</v>
       </c>
       <c r="P54" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q54">
         <v>4</v>
@@ -12303,7 +12312,7 @@
         <v>2</v>
       </c>
       <c r="AP54">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AQ54">
         <v>1.38</v>
@@ -12715,7 +12724,7 @@
         <v>0.5</v>
       </c>
       <c r="AP56">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ56">
         <v>1.33</v>
@@ -12843,7 +12852,7 @@
         <v>131</v>
       </c>
       <c r="P57" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q57">
         <v>3.25</v>
@@ -12921,10 +12930,10 @@
         <v>0</v>
       </c>
       <c r="AP57">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AQ57">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR57">
         <v>1.48</v>
@@ -13255,7 +13264,7 @@
         <v>133</v>
       </c>
       <c r="P59" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="Q59">
         <v>3.2</v>
@@ -13542,7 +13551,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ60">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR60">
         <v>1.79</v>
@@ -13748,7 +13757,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ61">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AR61">
         <v>1.6</v>
@@ -13873,7 +13882,7 @@
         <v>136</v>
       </c>
       <c r="P62" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q62">
         <v>3.4</v>
@@ -14079,7 +14088,7 @@
         <v>137</v>
       </c>
       <c r="P63" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q63">
         <v>2.38</v>
@@ -14285,7 +14294,7 @@
         <v>138</v>
       </c>
       <c r="P64" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q64">
         <v>4.75</v>
@@ -14697,7 +14706,7 @@
         <v>139</v>
       </c>
       <c r="P66" t="s">
-        <v>239</v>
+        <v>204</v>
       </c>
       <c r="Q66">
         <v>3.4</v>
@@ -14903,7 +14912,7 @@
         <v>90</v>
       </c>
       <c r="P67" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q67">
         <v>5.5</v>
@@ -14981,7 +14990,7 @@
         <v>1.5</v>
       </c>
       <c r="AP67">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AQ67">
         <v>1.78</v>
@@ -15109,7 +15118,7 @@
         <v>140</v>
       </c>
       <c r="P68" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q68">
         <v>1.73</v>
@@ -15190,7 +15199,7 @@
         <v>2.78</v>
       </c>
       <c r="AQ68">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR68">
         <v>2.38</v>
@@ -15315,7 +15324,7 @@
         <v>90</v>
       </c>
       <c r="P69" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q69">
         <v>4</v>
@@ -15521,7 +15530,7 @@
         <v>141</v>
       </c>
       <c r="P70" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q70">
         <v>2.1</v>
@@ -15727,7 +15736,7 @@
         <v>93</v>
       </c>
       <c r="P71" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q71">
         <v>3.6</v>
@@ -15933,7 +15942,7 @@
         <v>142</v>
       </c>
       <c r="P72" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q72">
         <v>3.1</v>
@@ -16139,7 +16148,7 @@
         <v>90</v>
       </c>
       <c r="P73" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q73">
         <v>4.33</v>
@@ -16426,7 +16435,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ74">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AR74">
         <v>1.65</v>
@@ -16551,7 +16560,7 @@
         <v>143</v>
       </c>
       <c r="P75" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q75">
         <v>3</v>
@@ -16629,7 +16638,7 @@
         <v>0.25</v>
       </c>
       <c r="AP75">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AQ75">
         <v>0.11</v>
@@ -16757,7 +16766,7 @@
         <v>144</v>
       </c>
       <c r="P76" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -16963,7 +16972,7 @@
         <v>90</v>
       </c>
       <c r="P77" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17169,7 +17178,7 @@
         <v>145</v>
       </c>
       <c r="P78" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q78">
         <v>2.1</v>
@@ -17250,7 +17259,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ78">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR78">
         <v>1.8</v>
@@ -17375,7 +17384,7 @@
         <v>90</v>
       </c>
       <c r="P79" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q79">
         <v>3.5</v>
@@ -17581,7 +17590,7 @@
         <v>146</v>
       </c>
       <c r="P80" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q80">
         <v>2.63</v>
@@ -17662,7 +17671,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ80">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR80">
         <v>1.34</v>
@@ -17993,7 +18002,7 @@
         <v>90</v>
       </c>
       <c r="P82" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q82">
         <v>3.6</v>
@@ -18071,7 +18080,7 @@
         <v>2</v>
       </c>
       <c r="AP82">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ82">
         <v>2.33</v>
@@ -18817,7 +18826,7 @@
         <v>90</v>
       </c>
       <c r="P86" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q86">
         <v>3.2</v>
@@ -19101,10 +19110,10 @@
         <v>0.5</v>
       </c>
       <c r="AP87">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AQ87">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR87">
         <v>1.3</v>
@@ -19847,7 +19856,7 @@
         <v>153</v>
       </c>
       <c r="P91" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q91">
         <v>4.33</v>
@@ -20053,7 +20062,7 @@
         <v>154</v>
       </c>
       <c r="P92" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q92">
         <v>1.91</v>
@@ -20131,10 +20140,10 @@
         <v>0.2</v>
       </c>
       <c r="AP92">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ92">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR92">
         <v>1.38</v>
@@ -20259,7 +20268,7 @@
         <v>144</v>
       </c>
       <c r="P93" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -20465,7 +20474,7 @@
         <v>155</v>
       </c>
       <c r="P94" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -20546,7 +20555,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ94">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR94">
         <v>1.78</v>
@@ -20671,7 +20680,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q95">
         <v>8.5</v>
@@ -20749,7 +20758,7 @@
         <v>2.2</v>
       </c>
       <c r="AP95">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AQ95">
         <v>2.33</v>
@@ -20877,7 +20886,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q96">
         <v>3.2</v>
@@ -21083,7 +21092,7 @@
         <v>90</v>
       </c>
       <c r="P97" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q97">
         <v>2.88</v>
@@ -21289,7 +21298,7 @@
         <v>158</v>
       </c>
       <c r="P98" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q98">
         <v>3.5</v>
@@ -21495,7 +21504,7 @@
         <v>90</v>
       </c>
       <c r="P99" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q99">
         <v>3.75</v>
@@ -21907,7 +21916,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q101">
         <v>2.05</v>
@@ -22319,7 +22328,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -22603,7 +22612,7 @@
         <v>0</v>
       </c>
       <c r="AP104">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AQ104">
         <v>0</v>
@@ -23349,7 +23358,7 @@
         <v>90</v>
       </c>
       <c r="P108" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q108">
         <v>2.6</v>
@@ -23430,7 +23439,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ108">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AR108">
         <v>1.38</v>
@@ -23555,7 +23564,7 @@
         <v>166</v>
       </c>
       <c r="P109" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q109">
         <v>2.38</v>
@@ -23636,7 +23645,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ109">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR109">
         <v>1.61</v>
@@ -23761,7 +23770,7 @@
         <v>90</v>
       </c>
       <c r="P110" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q110">
         <v>3.4</v>
@@ -24173,7 +24182,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q112">
         <v>2.88</v>
@@ -24254,7 +24263,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ112">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR112">
         <v>1.45</v>
@@ -24460,7 +24469,7 @@
         <v>2.78</v>
       </c>
       <c r="AQ113">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR113">
         <v>2.24</v>
@@ -24585,7 +24594,7 @@
         <v>170</v>
       </c>
       <c r="P114" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q114">
         <v>4.33</v>
@@ -24791,7 +24800,7 @@
         <v>90</v>
       </c>
       <c r="P115" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q115">
         <v>3</v>
@@ -25078,7 +25087,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ116">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR116">
         <v>1.39</v>
@@ -25203,7 +25212,7 @@
         <v>172</v>
       </c>
       <c r="P117" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q117">
         <v>2.6</v>
@@ -25409,7 +25418,7 @@
         <v>173</v>
       </c>
       <c r="P118" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q118">
         <v>3.1</v>
@@ -25487,7 +25496,7 @@
         <v>2.4</v>
       </c>
       <c r="AP118">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ118">
         <v>1.56</v>
@@ -26233,7 +26242,7 @@
         <v>176</v>
       </c>
       <c r="P122" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q122">
         <v>2.05</v>
@@ -26314,7 +26323,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ122">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AR122">
         <v>1.66</v>
@@ -26439,7 +26448,7 @@
         <v>90</v>
       </c>
       <c r="P123" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q123">
         <v>4.75</v>
@@ -26517,7 +26526,7 @@
         <v>1.5</v>
       </c>
       <c r="AP123">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AQ123">
         <v>1.33</v>
@@ -27263,7 +27272,7 @@
         <v>90</v>
       </c>
       <c r="P127" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q127">
         <v>5</v>
@@ -27341,7 +27350,7 @@
         <v>2.57</v>
       </c>
       <c r="AP127">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AQ127">
         <v>2.67</v>
@@ -27675,7 +27684,7 @@
         <v>148</v>
       </c>
       <c r="P129" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q129">
         <v>2.88</v>
@@ -27753,7 +27762,7 @@
         <v>1.71</v>
       </c>
       <c r="AP129">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ129">
         <v>1.56</v>
@@ -27881,7 +27890,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q130">
         <v>4.33</v>
@@ -28293,7 +28302,7 @@
         <v>181</v>
       </c>
       <c r="P132" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q132">
         <v>3.5</v>
@@ -28499,7 +28508,7 @@
         <v>90</v>
       </c>
       <c r="P133" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q133">
         <v>3.5</v>
@@ -28580,7 +28589,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ133">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR133">
         <v>1.14</v>
@@ -28786,7 +28795,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ134">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR134">
         <v>1.46</v>
@@ -29323,7 +29332,7 @@
         <v>185</v>
       </c>
       <c r="P137" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q137">
         <v>3.4</v>
@@ -29529,7 +29538,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q138">
         <v>2.88</v>
@@ -29735,7 +29744,7 @@
         <v>187</v>
       </c>
       <c r="P139" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q139">
         <v>4</v>
@@ -29813,7 +29822,7 @@
         <v>1.57</v>
       </c>
       <c r="AP139">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AQ139">
         <v>1.38</v>
@@ -29941,7 +29950,7 @@
         <v>129</v>
       </c>
       <c r="P140" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q140">
         <v>2.2</v>
@@ -30022,7 +30031,7 @@
         <v>2</v>
       </c>
       <c r="AQ140">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AR140">
         <v>1.36</v>
@@ -30640,7 +30649,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ143">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR143">
         <v>1.2</v>
@@ -30843,7 +30852,7 @@
         <v>0.43</v>
       </c>
       <c r="AP144">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AQ144">
         <v>0.67</v>
@@ -30971,7 +30980,7 @@
         <v>191</v>
       </c>
       <c r="P145" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q145">
         <v>1.8</v>
@@ -31049,10 +31058,10 @@
         <v>0.86</v>
       </c>
       <c r="AP145">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ145">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AR145">
         <v>1.34</v>
@@ -31177,7 +31186,7 @@
         <v>192</v>
       </c>
       <c r="P146" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q146">
         <v>4.33</v>
@@ -31589,7 +31598,7 @@
         <v>193</v>
       </c>
       <c r="P148" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q148">
         <v>3.6</v>
@@ -31795,7 +31804,7 @@
         <v>194</v>
       </c>
       <c r="P149" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q149">
         <v>3.2</v>
@@ -32001,7 +32010,7 @@
         <v>195</v>
       </c>
       <c r="P150" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q150">
         <v>3.5</v>
@@ -32207,7 +32216,7 @@
         <v>196</v>
       </c>
       <c r="P151" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q151">
         <v>5.25</v>
@@ -32413,7 +32422,7 @@
         <v>197</v>
       </c>
       <c r="P152" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q152">
         <v>2.6</v>
@@ -32619,7 +32628,7 @@
         <v>198</v>
       </c>
       <c r="P153" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q153">
         <v>2.3</v>
@@ -32700,7 +32709,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ153">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AR153">
         <v>1.39</v>
@@ -33031,7 +33040,7 @@
         <v>200</v>
       </c>
       <c r="P155" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q155">
         <v>5</v>
@@ -33443,7 +33452,7 @@
         <v>202</v>
       </c>
       <c r="P157" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33649,7 +33658,7 @@
         <v>203</v>
       </c>
       <c r="P158" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q158">
         <v>2.6</v>
@@ -34012,6 +34021,830 @@
       </c>
       <c r="BP159">
         <v>1.3</v>
+      </c>
+    </row>
+    <row r="160" spans="1:68">
+      <c r="A160" s="1">
+        <v>159</v>
+      </c>
+      <c r="B160">
+        <v>7468513</v>
+      </c>
+      <c r="C160" t="s">
+        <v>68</v>
+      </c>
+      <c r="D160" t="s">
+        <v>69</v>
+      </c>
+      <c r="E160" s="2">
+        <v>45676.45833333334</v>
+      </c>
+      <c r="F160">
+        <v>18</v>
+      </c>
+      <c r="G160" t="s">
+        <v>82</v>
+      </c>
+      <c r="H160" t="s">
+        <v>85</v>
+      </c>
+      <c r="I160">
+        <v>0</v>
+      </c>
+      <c r="J160">
+        <v>1</v>
+      </c>
+      <c r="K160">
+        <v>1</v>
+      </c>
+      <c r="L160">
+        <v>1</v>
+      </c>
+      <c r="M160">
+        <v>1</v>
+      </c>
+      <c r="N160">
+        <v>2</v>
+      </c>
+      <c r="O160" t="s">
+        <v>204</v>
+      </c>
+      <c r="P160" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q160">
+        <v>3.2</v>
+      </c>
+      <c r="R160">
+        <v>2.05</v>
+      </c>
+      <c r="S160">
+        <v>3.5</v>
+      </c>
+      <c r="T160">
+        <v>1.44</v>
+      </c>
+      <c r="U160">
+        <v>2.63</v>
+      </c>
+      <c r="V160">
+        <v>3.25</v>
+      </c>
+      <c r="W160">
+        <v>1.33</v>
+      </c>
+      <c r="X160">
+        <v>9</v>
+      </c>
+      <c r="Y160">
+        <v>1.07</v>
+      </c>
+      <c r="Z160">
+        <v>2.5</v>
+      </c>
+      <c r="AA160">
+        <v>3.2</v>
+      </c>
+      <c r="AB160">
+        <v>2.84</v>
+      </c>
+      <c r="AC160">
+        <v>1.07</v>
+      </c>
+      <c r="AD160">
+        <v>10</v>
+      </c>
+      <c r="AE160">
+        <v>1.36</v>
+      </c>
+      <c r="AF160">
+        <v>3.2</v>
+      </c>
+      <c r="AG160">
+        <v>2.02</v>
+      </c>
+      <c r="AH160">
+        <v>1.74</v>
+      </c>
+      <c r="AI160">
+        <v>1.8</v>
+      </c>
+      <c r="AJ160">
+        <v>1.95</v>
+      </c>
+      <c r="AK160">
+        <v>1.43</v>
+      </c>
+      <c r="AL160">
+        <v>1.33</v>
+      </c>
+      <c r="AM160">
+        <v>1.47</v>
+      </c>
+      <c r="AN160">
+        <v>1.88</v>
+      </c>
+      <c r="AO160">
+        <v>0.78</v>
+      </c>
+      <c r="AP160">
+        <v>1.78</v>
+      </c>
+      <c r="AQ160">
+        <v>0.8</v>
+      </c>
+      <c r="AR160">
+        <v>1.21</v>
+      </c>
+      <c r="AS160">
+        <v>1.12</v>
+      </c>
+      <c r="AT160">
+        <v>2.33</v>
+      </c>
+      <c r="AU160">
+        <v>4</v>
+      </c>
+      <c r="AV160">
+        <v>5</v>
+      </c>
+      <c r="AW160">
+        <v>11</v>
+      </c>
+      <c r="AX160">
+        <v>4</v>
+      </c>
+      <c r="AY160">
+        <v>19</v>
+      </c>
+      <c r="AZ160">
+        <v>12</v>
+      </c>
+      <c r="BA160">
+        <v>7</v>
+      </c>
+      <c r="BB160">
+        <v>7</v>
+      </c>
+      <c r="BC160">
+        <v>14</v>
+      </c>
+      <c r="BD160">
+        <v>2.1</v>
+      </c>
+      <c r="BE160">
+        <v>6.4</v>
+      </c>
+      <c r="BF160">
+        <v>1.9</v>
+      </c>
+      <c r="BG160">
+        <v>1.29</v>
+      </c>
+      <c r="BH160">
+        <v>3.15</v>
+      </c>
+      <c r="BI160">
+        <v>1.5</v>
+      </c>
+      <c r="BJ160">
+        <v>2.35</v>
+      </c>
+      <c r="BK160">
+        <v>1.82</v>
+      </c>
+      <c r="BL160">
+        <v>1.86</v>
+      </c>
+      <c r="BM160">
+        <v>2.3</v>
+      </c>
+      <c r="BN160">
+        <v>1.54</v>
+      </c>
+      <c r="BO160">
+        <v>2.95</v>
+      </c>
+      <c r="BP160">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="161" spans="1:68">
+      <c r="A161" s="1">
+        <v>160</v>
+      </c>
+      <c r="B161">
+        <v>7468516</v>
+      </c>
+      <c r="C161" t="s">
+        <v>68</v>
+      </c>
+      <c r="D161" t="s">
+        <v>69</v>
+      </c>
+      <c r="E161" s="2">
+        <v>45676.55208333334</v>
+      </c>
+      <c r="F161">
+        <v>18</v>
+      </c>
+      <c r="G161" t="s">
+        <v>77</v>
+      </c>
+      <c r="H161" t="s">
+        <v>74</v>
+      </c>
+      <c r="I161">
+        <v>1</v>
+      </c>
+      <c r="J161">
+        <v>0</v>
+      </c>
+      <c r="K161">
+        <v>1</v>
+      </c>
+      <c r="L161">
+        <v>2</v>
+      </c>
+      <c r="M161">
+        <v>0</v>
+      </c>
+      <c r="N161">
+        <v>2</v>
+      </c>
+      <c r="O161" t="s">
+        <v>205</v>
+      </c>
+      <c r="P161" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q161">
+        <v>3.1</v>
+      </c>
+      <c r="R161">
+        <v>2.1</v>
+      </c>
+      <c r="S161">
+        <v>3.5</v>
+      </c>
+      <c r="T161">
+        <v>1.4</v>
+      </c>
+      <c r="U161">
+        <v>2.75</v>
+      </c>
+      <c r="V161">
+        <v>3</v>
+      </c>
+      <c r="W161">
+        <v>1.36</v>
+      </c>
+      <c r="X161">
+        <v>8</v>
+      </c>
+      <c r="Y161">
+        <v>1.08</v>
+      </c>
+      <c r="Z161">
+        <v>2.6</v>
+      </c>
+      <c r="AA161">
+        <v>3.25</v>
+      </c>
+      <c r="AB161">
+        <v>2.75</v>
+      </c>
+      <c r="AC161">
+        <v>1.06</v>
+      </c>
+      <c r="AD161">
+        <v>10</v>
+      </c>
+      <c r="AE161">
+        <v>1.32</v>
+      </c>
+      <c r="AF161">
+        <v>3.4</v>
+      </c>
+      <c r="AG161">
+        <v>1.86</v>
+      </c>
+      <c r="AH161">
+        <v>1.94</v>
+      </c>
+      <c r="AI161">
+        <v>1.75</v>
+      </c>
+      <c r="AJ161">
+        <v>2</v>
+      </c>
+      <c r="AK161">
+        <v>1.41</v>
+      </c>
+      <c r="AL161">
+        <v>1.32</v>
+      </c>
+      <c r="AM161">
+        <v>1.52</v>
+      </c>
+      <c r="AN161">
+        <v>0.88</v>
+      </c>
+      <c r="AO161">
+        <v>0.5</v>
+      </c>
+      <c r="AP161">
+        <v>1.11</v>
+      </c>
+      <c r="AQ161">
+        <v>0.44</v>
+      </c>
+      <c r="AR161">
+        <v>1.21</v>
+      </c>
+      <c r="AS161">
+        <v>1.18</v>
+      </c>
+      <c r="AT161">
+        <v>2.39</v>
+      </c>
+      <c r="AU161">
+        <v>7</v>
+      </c>
+      <c r="AV161">
+        <v>5</v>
+      </c>
+      <c r="AW161">
+        <v>8</v>
+      </c>
+      <c r="AX161">
+        <v>6</v>
+      </c>
+      <c r="AY161">
+        <v>17</v>
+      </c>
+      <c r="AZ161">
+        <v>11</v>
+      </c>
+      <c r="BA161">
+        <v>4</v>
+      </c>
+      <c r="BB161">
+        <v>2</v>
+      </c>
+      <c r="BC161">
+        <v>6</v>
+      </c>
+      <c r="BD161">
+        <v>1.77</v>
+      </c>
+      <c r="BE161">
+        <v>6.25</v>
+      </c>
+      <c r="BF161">
+        <v>2.3</v>
+      </c>
+      <c r="BG161">
+        <v>1.43</v>
+      </c>
+      <c r="BH161">
+        <v>2.6</v>
+      </c>
+      <c r="BI161">
+        <v>1.7</v>
+      </c>
+      <c r="BJ161">
+        <v>2</v>
+      </c>
+      <c r="BK161">
+        <v>2.12</v>
+      </c>
+      <c r="BL161">
+        <v>1.63</v>
+      </c>
+      <c r="BM161">
+        <v>2.7</v>
+      </c>
+      <c r="BN161">
+        <v>1.38</v>
+      </c>
+      <c r="BO161">
+        <v>3.65</v>
+      </c>
+      <c r="BP161">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="162" spans="1:68">
+      <c r="A162" s="1">
+        <v>161</v>
+      </c>
+      <c r="B162">
+        <v>7468515</v>
+      </c>
+      <c r="C162" t="s">
+        <v>68</v>
+      </c>
+      <c r="D162" t="s">
+        <v>69</v>
+      </c>
+      <c r="E162" s="2">
+        <v>45676.55208333334</v>
+      </c>
+      <c r="F162">
+        <v>18</v>
+      </c>
+      <c r="G162" t="s">
+        <v>72</v>
+      </c>
+      <c r="H162" t="s">
+        <v>70</v>
+      </c>
+      <c r="I162">
+        <v>1</v>
+      </c>
+      <c r="J162">
+        <v>0</v>
+      </c>
+      <c r="K162">
+        <v>1</v>
+      </c>
+      <c r="L162">
+        <v>1</v>
+      </c>
+      <c r="M162">
+        <v>1</v>
+      </c>
+      <c r="N162">
+        <v>2</v>
+      </c>
+      <c r="O162" t="s">
+        <v>206</v>
+      </c>
+      <c r="P162" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q162">
+        <v>2.3</v>
+      </c>
+      <c r="R162">
+        <v>2.2</v>
+      </c>
+      <c r="S162">
+        <v>5.5</v>
+      </c>
+      <c r="T162">
+        <v>1.4</v>
+      </c>
+      <c r="U162">
+        <v>2.75</v>
+      </c>
+      <c r="V162">
+        <v>3</v>
+      </c>
+      <c r="W162">
+        <v>1.36</v>
+      </c>
+      <c r="X162">
+        <v>8</v>
+      </c>
+      <c r="Y162">
+        <v>1.08</v>
+      </c>
+      <c r="Z162">
+        <v>1.7</v>
+      </c>
+      <c r="AA162">
+        <v>3.75</v>
+      </c>
+      <c r="AB162">
+        <v>5</v>
+      </c>
+      <c r="AC162">
+        <v>1.05</v>
+      </c>
+      <c r="AD162">
+        <v>12</v>
+      </c>
+      <c r="AE162">
+        <v>1.32</v>
+      </c>
+      <c r="AF162">
+        <v>3.4</v>
+      </c>
+      <c r="AG162">
+        <v>1.95</v>
+      </c>
+      <c r="AH162">
+        <v>1.85</v>
+      </c>
+      <c r="AI162">
+        <v>1.95</v>
+      </c>
+      <c r="AJ162">
+        <v>1.8</v>
+      </c>
+      <c r="AK162">
+        <v>1.16</v>
+      </c>
+      <c r="AL162">
+        <v>1.27</v>
+      </c>
+      <c r="AM162">
+        <v>2.15</v>
+      </c>
+      <c r="AN162">
+        <v>1</v>
+      </c>
+      <c r="AO162">
+        <v>0.75</v>
+      </c>
+      <c r="AP162">
+        <v>1</v>
+      </c>
+      <c r="AQ162">
+        <v>0.78</v>
+      </c>
+      <c r="AR162">
+        <v>1.2</v>
+      </c>
+      <c r="AS162">
+        <v>0.91</v>
+      </c>
+      <c r="AT162">
+        <v>2.11</v>
+      </c>
+      <c r="AU162">
+        <v>4</v>
+      </c>
+      <c r="AV162">
+        <v>3</v>
+      </c>
+      <c r="AW162">
+        <v>6</v>
+      </c>
+      <c r="AX162">
+        <v>3</v>
+      </c>
+      <c r="AY162">
+        <v>12</v>
+      </c>
+      <c r="AZ162">
+        <v>6</v>
+      </c>
+      <c r="BA162">
+        <v>6</v>
+      </c>
+      <c r="BB162">
+        <v>6</v>
+      </c>
+      <c r="BC162">
+        <v>12</v>
+      </c>
+      <c r="BD162">
+        <v>1.46</v>
+      </c>
+      <c r="BE162">
+        <v>6.75</v>
+      </c>
+      <c r="BF162">
+        <v>3.05</v>
+      </c>
+      <c r="BG162">
+        <v>1.38</v>
+      </c>
+      <c r="BH162">
+        <v>2.7</v>
+      </c>
+      <c r="BI162">
+        <v>1.67</v>
+      </c>
+      <c r="BJ162">
+        <v>2.05</v>
+      </c>
+      <c r="BK162">
+        <v>2.07</v>
+      </c>
+      <c r="BL162">
+        <v>1.66</v>
+      </c>
+      <c r="BM162">
+        <v>2.65</v>
+      </c>
+      <c r="BN162">
+        <v>1.41</v>
+      </c>
+      <c r="BO162">
+        <v>3.55</v>
+      </c>
+      <c r="BP162">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="163" spans="1:68">
+      <c r="A163" s="1">
+        <v>162</v>
+      </c>
+      <c r="B163">
+        <v>7468509</v>
+      </c>
+      <c r="C163" t="s">
+        <v>68</v>
+      </c>
+      <c r="D163" t="s">
+        <v>69</v>
+      </c>
+      <c r="E163" s="2">
+        <v>45676.69791666666</v>
+      </c>
+      <c r="F163">
+        <v>18</v>
+      </c>
+      <c r="G163" t="s">
+        <v>87</v>
+      </c>
+      <c r="H163" t="s">
+        <v>84</v>
+      </c>
+      <c r="I163">
+        <v>0</v>
+      </c>
+      <c r="J163">
+        <v>1</v>
+      </c>
+      <c r="K163">
+        <v>1</v>
+      </c>
+      <c r="L163">
+        <v>1</v>
+      </c>
+      <c r="M163">
+        <v>1</v>
+      </c>
+      <c r="N163">
+        <v>2</v>
+      </c>
+      <c r="O163" t="s">
+        <v>207</v>
+      </c>
+      <c r="P163" t="s">
+        <v>296</v>
+      </c>
+      <c r="Q163">
+        <v>2.05</v>
+      </c>
+      <c r="R163">
+        <v>2.5</v>
+      </c>
+      <c r="S163">
+        <v>5</v>
+      </c>
+      <c r="T163">
+        <v>1.29</v>
+      </c>
+      <c r="U163">
+        <v>3.5</v>
+      </c>
+      <c r="V163">
+        <v>2.38</v>
+      </c>
+      <c r="W163">
+        <v>1.53</v>
+      </c>
+      <c r="X163">
+        <v>5.5</v>
+      </c>
+      <c r="Y163">
+        <v>1.14</v>
+      </c>
+      <c r="Z163">
+        <v>1.45</v>
+      </c>
+      <c r="AA163">
+        <v>4.5</v>
+      </c>
+      <c r="AB163">
+        <v>6.5</v>
+      </c>
+      <c r="AC163">
+        <v>1.02</v>
+      </c>
+      <c r="AD163">
+        <v>19</v>
+      </c>
+      <c r="AE163">
+        <v>1.18</v>
+      </c>
+      <c r="AF163">
+        <v>5</v>
+      </c>
+      <c r="AG163">
+        <v>1.55</v>
+      </c>
+      <c r="AH163">
+        <v>2.3</v>
+      </c>
+      <c r="AI163">
+        <v>1.67</v>
+      </c>
+      <c r="AJ163">
+        <v>2.1</v>
+      </c>
+      <c r="AK163">
+        <v>1.15</v>
+      </c>
+      <c r="AL163">
+        <v>1.21</v>
+      </c>
+      <c r="AM163">
+        <v>2.35</v>
+      </c>
+      <c r="AN163">
+        <v>1.5</v>
+      </c>
+      <c r="AO163">
+        <v>0.89</v>
+      </c>
+      <c r="AP163">
+        <v>1.44</v>
+      </c>
+      <c r="AQ163">
+        <v>0.9</v>
+      </c>
+      <c r="AR163">
+        <v>1.45</v>
+      </c>
+      <c r="AS163">
+        <v>1.29</v>
+      </c>
+      <c r="AT163">
+        <v>2.74</v>
+      </c>
+      <c r="AU163">
+        <v>4</v>
+      </c>
+      <c r="AV163">
+        <v>4</v>
+      </c>
+      <c r="AW163">
+        <v>14</v>
+      </c>
+      <c r="AX163">
+        <v>5</v>
+      </c>
+      <c r="AY163">
+        <v>24</v>
+      </c>
+      <c r="AZ163">
+        <v>11</v>
+      </c>
+      <c r="BA163">
+        <v>9</v>
+      </c>
+      <c r="BB163">
+        <v>3</v>
+      </c>
+      <c r="BC163">
+        <v>12</v>
+      </c>
+      <c r="BD163">
+        <v>1.44</v>
+      </c>
+      <c r="BE163">
+        <v>6.75</v>
+      </c>
+      <c r="BF163">
+        <v>3.15</v>
+      </c>
+      <c r="BG163">
+        <v>1.47</v>
+      </c>
+      <c r="BH163">
+        <v>2.48</v>
+      </c>
+      <c r="BI163">
+        <v>1.79</v>
+      </c>
+      <c r="BJ163">
+        <v>1.9</v>
+      </c>
+      <c r="BK163">
+        <v>2.25</v>
+      </c>
+      <c r="BL163">
+        <v>1.55</v>
+      </c>
+      <c r="BM163">
+        <v>2.9</v>
+      </c>
+      <c r="BN163">
+        <v>1.34</v>
+      </c>
+      <c r="BO163">
+        <v>3.9</v>
+      </c>
+      <c r="BP163">
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/France Ligue 1_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/France Ligue 1_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1046" uniqueCount="298">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -638,6 +638,9 @@
   </si>
   <si>
     <t>['68']</t>
+  </si>
+  <si>
+    <t>['27']</t>
   </si>
   <si>
     <t>['3', '84', '86', '90']</t>
@@ -1266,7 +1269,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP163"/>
+  <dimension ref="A1:BP164"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1522,7 +1525,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q2">
         <v>6</v>
@@ -1728,7 +1731,7 @@
         <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q3">
         <v>3.4</v>
@@ -1934,7 +1937,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -2221,7 +2224,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ5">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2346,7 +2349,7 @@
         <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q6">
         <v>3.75</v>
@@ -2424,7 +2427,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ6">
         <v>1.2</v>
@@ -2552,7 +2555,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q7">
         <v>2.75</v>
@@ -3582,7 +3585,7 @@
         <v>90</v>
       </c>
       <c r="P12" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q12">
         <v>2.8</v>
@@ -3994,7 +3997,7 @@
         <v>90</v>
       </c>
       <c r="P14" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q14">
         <v>2.65</v>
@@ -4406,7 +4409,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q16">
         <v>3.6</v>
@@ -5024,7 +5027,7 @@
         <v>101</v>
       </c>
       <c r="P19" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q19">
         <v>2.1</v>
@@ -5230,7 +5233,7 @@
         <v>102</v>
       </c>
       <c r="P20" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q20">
         <v>2.45</v>
@@ -5517,7 +5520,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ21">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AR21">
         <v>1.56</v>
@@ -5642,7 +5645,7 @@
         <v>104</v>
       </c>
       <c r="P22" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q22">
         <v>2.8</v>
@@ -5848,7 +5851,7 @@
         <v>105</v>
       </c>
       <c r="P23" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q23">
         <v>4.2</v>
@@ -6054,7 +6057,7 @@
         <v>106</v>
       </c>
       <c r="P24" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q24">
         <v>2.4</v>
@@ -6260,7 +6263,7 @@
         <v>93</v>
       </c>
       <c r="P25" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q25">
         <v>4.5</v>
@@ -6672,7 +6675,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q27">
         <v>3.4</v>
@@ -6878,7 +6881,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q28">
         <v>4.33</v>
@@ -7496,7 +7499,7 @@
         <v>90</v>
       </c>
       <c r="P31" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q31">
         <v>3.75</v>
@@ -7574,7 +7577,7 @@
         <v>3</v>
       </c>
       <c r="AP31">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ31">
         <v>1.56</v>
@@ -8114,7 +8117,7 @@
         <v>114</v>
       </c>
       <c r="P34" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q34">
         <v>2.3</v>
@@ -8320,7 +8323,7 @@
         <v>91</v>
       </c>
       <c r="P35" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q35">
         <v>3</v>
@@ -9019,7 +9022,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ38">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AR38">
         <v>1.16</v>
@@ -9144,7 +9147,7 @@
         <v>117</v>
       </c>
       <c r="P39" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q39">
         <v>2.2</v>
@@ -9350,7 +9353,7 @@
         <v>118</v>
       </c>
       <c r="P40" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q40">
         <v>3</v>
@@ -10174,7 +10177,7 @@
         <v>118</v>
       </c>
       <c r="P44" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q44">
         <v>3.75</v>
@@ -10380,7 +10383,7 @@
         <v>122</v>
       </c>
       <c r="P45" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q45">
         <v>2.88</v>
@@ -10586,7 +10589,7 @@
         <v>123</v>
       </c>
       <c r="P46" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q46">
         <v>3.25</v>
@@ -10870,7 +10873,7 @@
         <v>0</v>
       </c>
       <c r="AP47">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ47">
         <v>0.67</v>
@@ -10998,7 +11001,7 @@
         <v>125</v>
       </c>
       <c r="P48" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q48">
         <v>1.83</v>
@@ -11410,7 +11413,7 @@
         <v>90</v>
       </c>
       <c r="P50" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q50">
         <v>5</v>
@@ -11616,7 +11619,7 @@
         <v>126</v>
       </c>
       <c r="P51" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q51">
         <v>1.8</v>
@@ -11822,7 +11825,7 @@
         <v>127</v>
       </c>
       <c r="P52" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q52">
         <v>3.1</v>
@@ -12028,7 +12031,7 @@
         <v>128</v>
       </c>
       <c r="P53" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q53">
         <v>2.3</v>
@@ -12109,7 +12112,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ53">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AR53">
         <v>1.5</v>
@@ -12234,7 +12237,7 @@
         <v>106</v>
       </c>
       <c r="P54" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q54">
         <v>4</v>
@@ -12852,7 +12855,7 @@
         <v>131</v>
       </c>
       <c r="P57" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q57">
         <v>3.25</v>
@@ -13264,7 +13267,7 @@
         <v>133</v>
       </c>
       <c r="P59" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q59">
         <v>3.2</v>
@@ -13882,7 +13885,7 @@
         <v>136</v>
       </c>
       <c r="P62" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q62">
         <v>3.4</v>
@@ -14088,7 +14091,7 @@
         <v>137</v>
       </c>
       <c r="P63" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q63">
         <v>2.38</v>
@@ -14294,7 +14297,7 @@
         <v>138</v>
       </c>
       <c r="P64" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q64">
         <v>4.75</v>
@@ -14912,7 +14915,7 @@
         <v>90</v>
       </c>
       <c r="P67" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q67">
         <v>5.5</v>
@@ -15118,7 +15121,7 @@
         <v>140</v>
       </c>
       <c r="P68" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q68">
         <v>1.73</v>
@@ -15324,7 +15327,7 @@
         <v>90</v>
       </c>
       <c r="P69" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q69">
         <v>4</v>
@@ -15530,7 +15533,7 @@
         <v>141</v>
       </c>
       <c r="P70" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q70">
         <v>2.1</v>
@@ -15736,7 +15739,7 @@
         <v>93</v>
       </c>
       <c r="P71" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q71">
         <v>3.6</v>
@@ -15942,7 +15945,7 @@
         <v>142</v>
       </c>
       <c r="P72" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q72">
         <v>3.1</v>
@@ -16020,7 +16023,7 @@
         <v>2.33</v>
       </c>
       <c r="AP72">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ72">
         <v>1.38</v>
@@ -16148,7 +16151,7 @@
         <v>90</v>
       </c>
       <c r="P73" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q73">
         <v>4.33</v>
@@ -16560,7 +16563,7 @@
         <v>143</v>
       </c>
       <c r="P75" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q75">
         <v>3</v>
@@ -16641,7 +16644,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ75">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AR75">
         <v>1.25</v>
@@ -16766,7 +16769,7 @@
         <v>144</v>
       </c>
       <c r="P76" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q76">
         <v>3</v>
@@ -16972,7 +16975,7 @@
         <v>90</v>
       </c>
       <c r="P77" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17178,7 +17181,7 @@
         <v>145</v>
       </c>
       <c r="P78" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q78">
         <v>2.1</v>
@@ -17384,7 +17387,7 @@
         <v>90</v>
       </c>
       <c r="P79" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q79">
         <v>3.5</v>
@@ -17590,7 +17593,7 @@
         <v>146</v>
       </c>
       <c r="P80" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q80">
         <v>2.63</v>
@@ -18002,7 +18005,7 @@
         <v>90</v>
       </c>
       <c r="P82" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q82">
         <v>3.6</v>
@@ -18826,7 +18829,7 @@
         <v>90</v>
       </c>
       <c r="P86" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q86">
         <v>3.2</v>
@@ -19522,7 +19525,7 @@
         <v>0.25</v>
       </c>
       <c r="AP89">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ89">
         <v>0.13</v>
@@ -19856,7 +19859,7 @@
         <v>153</v>
       </c>
       <c r="P91" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q91">
         <v>4.33</v>
@@ -20062,7 +20065,7 @@
         <v>154</v>
       </c>
       <c r="P92" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q92">
         <v>1.91</v>
@@ -20268,7 +20271,7 @@
         <v>144</v>
       </c>
       <c r="P93" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -20474,7 +20477,7 @@
         <v>155</v>
       </c>
       <c r="P94" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -20680,7 +20683,7 @@
         <v>156</v>
       </c>
       <c r="P95" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q95">
         <v>8.5</v>
@@ -20886,7 +20889,7 @@
         <v>157</v>
       </c>
       <c r="P96" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q96">
         <v>3.2</v>
@@ -21092,7 +21095,7 @@
         <v>90</v>
       </c>
       <c r="P97" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q97">
         <v>2.88</v>
@@ -21298,7 +21301,7 @@
         <v>158</v>
       </c>
       <c r="P98" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q98">
         <v>3.5</v>
@@ -21504,7 +21507,7 @@
         <v>90</v>
       </c>
       <c r="P99" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q99">
         <v>3.75</v>
@@ -21791,7 +21794,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ100">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AR100">
         <v>1.78</v>
@@ -21916,7 +21919,7 @@
         <v>159</v>
       </c>
       <c r="P101" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q101">
         <v>2.05</v>
@@ -22328,7 +22331,7 @@
         <v>161</v>
       </c>
       <c r="P103" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q103">
         <v>2.88</v>
@@ -23230,7 +23233,7 @@
         <v>1.2</v>
       </c>
       <c r="AP107">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ107">
         <v>1.33</v>
@@ -23358,7 +23361,7 @@
         <v>90</v>
       </c>
       <c r="P108" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q108">
         <v>2.6</v>
@@ -23564,7 +23567,7 @@
         <v>166</v>
       </c>
       <c r="P109" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q109">
         <v>2.38</v>
@@ -23770,7 +23773,7 @@
         <v>90</v>
       </c>
       <c r="P110" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q110">
         <v>3.4</v>
@@ -24057,7 +24060,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ111">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AR111">
         <v>1.53</v>
@@ -24182,7 +24185,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q112">
         <v>2.88</v>
@@ -24594,7 +24597,7 @@
         <v>170</v>
       </c>
       <c r="P114" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q114">
         <v>4.33</v>
@@ -24800,7 +24803,7 @@
         <v>90</v>
       </c>
       <c r="P115" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q115">
         <v>3</v>
@@ -25212,7 +25215,7 @@
         <v>172</v>
       </c>
       <c r="P117" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q117">
         <v>2.6</v>
@@ -25418,7 +25421,7 @@
         <v>173</v>
       </c>
       <c r="P118" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q118">
         <v>3.1</v>
@@ -25908,7 +25911,7 @@
         <v>2.33</v>
       </c>
       <c r="AP120">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ120">
         <v>2.33</v>
@@ -26242,7 +26245,7 @@
         <v>176</v>
       </c>
       <c r="P122" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q122">
         <v>2.05</v>
@@ -26448,7 +26451,7 @@
         <v>90</v>
       </c>
       <c r="P123" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q123">
         <v>4.75</v>
@@ -27272,7 +27275,7 @@
         <v>90</v>
       </c>
       <c r="P127" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q127">
         <v>5</v>
@@ -27559,7 +27562,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ128">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AR128">
         <v>1.4</v>
@@ -27684,7 +27687,7 @@
         <v>148</v>
       </c>
       <c r="P129" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q129">
         <v>2.88</v>
@@ -27890,7 +27893,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q130">
         <v>4.33</v>
@@ -27968,7 +27971,7 @@
         <v>1.71</v>
       </c>
       <c r="AP130">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ130">
         <v>1.78</v>
@@ -28302,7 +28305,7 @@
         <v>181</v>
       </c>
       <c r="P132" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q132">
         <v>3.5</v>
@@ -28508,7 +28511,7 @@
         <v>90</v>
       </c>
       <c r="P133" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q133">
         <v>3.5</v>
@@ -29332,7 +29335,7 @@
         <v>185</v>
       </c>
       <c r="P137" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q137">
         <v>3.4</v>
@@ -29538,7 +29541,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q138">
         <v>2.88</v>
@@ -29744,7 +29747,7 @@
         <v>187</v>
       </c>
       <c r="P139" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q139">
         <v>4</v>
@@ -29950,7 +29953,7 @@
         <v>129</v>
       </c>
       <c r="P140" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q140">
         <v>2.2</v>
@@ -30980,7 +30983,7 @@
         <v>191</v>
       </c>
       <c r="P145" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q145">
         <v>1.8</v>
@@ -31186,7 +31189,7 @@
         <v>192</v>
       </c>
       <c r="P146" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q146">
         <v>4.33</v>
@@ -31470,7 +31473,7 @@
         <v>1.63</v>
       </c>
       <c r="AP147">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ147">
         <v>1.56</v>
@@ -31598,7 +31601,7 @@
         <v>193</v>
       </c>
       <c r="P148" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q148">
         <v>3.6</v>
@@ -31804,7 +31807,7 @@
         <v>194</v>
       </c>
       <c r="P149" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q149">
         <v>3.2</v>
@@ -32010,7 +32013,7 @@
         <v>195</v>
       </c>
       <c r="P150" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q150">
         <v>3.5</v>
@@ -32216,7 +32219,7 @@
         <v>196</v>
       </c>
       <c r="P151" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q151">
         <v>5.25</v>
@@ -32422,7 +32425,7 @@
         <v>197</v>
       </c>
       <c r="P152" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q152">
         <v>2.6</v>
@@ -32628,7 +32631,7 @@
         <v>198</v>
       </c>
       <c r="P153" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q153">
         <v>2.3</v>
@@ -32915,7 +32918,7 @@
         <v>2.78</v>
       </c>
       <c r="AQ154">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AR154">
         <v>2.26</v>
@@ -33040,7 +33043,7 @@
         <v>200</v>
       </c>
       <c r="P155" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q155">
         <v>5</v>
@@ -33452,7 +33455,7 @@
         <v>202</v>
       </c>
       <c r="P157" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q157">
         <v>4.33</v>
@@ -33658,7 +33661,7 @@
         <v>203</v>
       </c>
       <c r="P158" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q158">
         <v>2.6</v>
@@ -34688,7 +34691,7 @@
         <v>207</v>
       </c>
       <c r="P163" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q163">
         <v>2.05</v>
@@ -34845,6 +34848,212 @@
       </c>
       <c r="BP163">
         <v>1.2</v>
+      </c>
+    </row>
+    <row r="164" spans="1:68">
+      <c r="A164" s="1">
+        <v>163</v>
+      </c>
+      <c r="B164">
+        <v>7468523</v>
+      </c>
+      <c r="C164" t="s">
+        <v>68</v>
+      </c>
+      <c r="D164" t="s">
+        <v>69</v>
+      </c>
+      <c r="E164" s="2">
+        <v>45681.69791666666</v>
+      </c>
+      <c r="F164">
+        <v>19</v>
+      </c>
+      <c r="G164" t="s">
+        <v>74</v>
+      </c>
+      <c r="H164" t="s">
+        <v>82</v>
+      </c>
+      <c r="I164">
+        <v>1</v>
+      </c>
+      <c r="J164">
+        <v>1</v>
+      </c>
+      <c r="K164">
+        <v>2</v>
+      </c>
+      <c r="L164">
+        <v>1</v>
+      </c>
+      <c r="M164">
+        <v>1</v>
+      </c>
+      <c r="N164">
+        <v>2</v>
+      </c>
+      <c r="O164" t="s">
+        <v>208</v>
+      </c>
+      <c r="P164" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q164">
+        <v>2.5</v>
+      </c>
+      <c r="R164">
+        <v>2.25</v>
+      </c>
+      <c r="S164">
+        <v>4.33</v>
+      </c>
+      <c r="T164">
+        <v>1.36</v>
+      </c>
+      <c r="U164">
+        <v>3</v>
+      </c>
+      <c r="V164">
+        <v>2.63</v>
+      </c>
+      <c r="W164">
+        <v>1.44</v>
+      </c>
+      <c r="X164">
+        <v>7</v>
+      </c>
+      <c r="Y164">
+        <v>1.1</v>
+      </c>
+      <c r="Z164">
+        <v>1.86</v>
+      </c>
+      <c r="AA164">
+        <v>3.91</v>
+      </c>
+      <c r="AB164">
+        <v>4.2</v>
+      </c>
+      <c r="AC164">
+        <v>1.04</v>
+      </c>
+      <c r="AD164">
+        <v>13</v>
+      </c>
+      <c r="AE164">
+        <v>1.26</v>
+      </c>
+      <c r="AF164">
+        <v>4</v>
+      </c>
+      <c r="AG164">
+        <v>1.81</v>
+      </c>
+      <c r="AH164">
+        <v>2.01</v>
+      </c>
+      <c r="AI164">
+        <v>1.67</v>
+      </c>
+      <c r="AJ164">
+        <v>2.1</v>
+      </c>
+      <c r="AK164">
+        <v>1.26</v>
+      </c>
+      <c r="AL164">
+        <v>1.27</v>
+      </c>
+      <c r="AM164">
+        <v>1.85</v>
+      </c>
+      <c r="AN164">
+        <v>2</v>
+      </c>
+      <c r="AO164">
+        <v>0.11</v>
+      </c>
+      <c r="AP164">
+        <v>1.9</v>
+      </c>
+      <c r="AQ164">
+        <v>0.2</v>
+      </c>
+      <c r="AR164">
+        <v>1.3</v>
+      </c>
+      <c r="AS164">
+        <v>0.99</v>
+      </c>
+      <c r="AT164">
+        <v>2.29</v>
+      </c>
+      <c r="AU164">
+        <v>6</v>
+      </c>
+      <c r="AV164">
+        <v>2</v>
+      </c>
+      <c r="AW164">
+        <v>5</v>
+      </c>
+      <c r="AX164">
+        <v>6</v>
+      </c>
+      <c r="AY164">
+        <v>12</v>
+      </c>
+      <c r="AZ164">
+        <v>11</v>
+      </c>
+      <c r="BA164">
+        <v>3</v>
+      </c>
+      <c r="BB164">
+        <v>4</v>
+      </c>
+      <c r="BC164">
+        <v>7</v>
+      </c>
+      <c r="BD164">
+        <v>1.55</v>
+      </c>
+      <c r="BE164">
+        <v>6.4</v>
+      </c>
+      <c r="BF164">
+        <v>2.8</v>
+      </c>
+      <c r="BG164">
+        <v>1.36</v>
+      </c>
+      <c r="BH164">
+        <v>2.8</v>
+      </c>
+      <c r="BI164">
+        <v>1.63</v>
+      </c>
+      <c r="BJ164">
+        <v>2.12</v>
+      </c>
+      <c r="BK164">
+        <v>2</v>
+      </c>
+      <c r="BL164">
+        <v>1.71</v>
+      </c>
+      <c r="BM164">
+        <v>2.55</v>
+      </c>
+      <c r="BN164">
+        <v>1.44</v>
+      </c>
+      <c r="BO164">
+        <v>3.3</v>
+      </c>
+      <c r="BP164">
+        <v>1.27</v>
       </c>
     </row>
   </sheetData>
